--- a/5_simulation/outputs/tables/supplementary/S7_score_degradation_draws.xlsx
+++ b/5_simulation/outputs/tables/supplementary/S7_score_degradation_draws.xlsx
@@ -517,46 +517,46 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.312575415714</v>
+        <v>0.3125754157140549</v>
       </c>
       <c r="E2" t="n">
-        <v>0.312575415714</v>
+        <v>0.3125754157140546</v>
       </c>
       <c r="F2" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518178</v>
       </c>
       <c r="G2" t="n">
-        <v>24.1408606813</v>
+        <v>24.20043623911963</v>
       </c>
       <c r="H2" t="n">
-        <v>7.37737860552</v>
+        <v>7.383858090465624</v>
       </c>
       <c r="I2" t="n">
-        <v>3.30619796029</v>
+        <v>3.309258326416882</v>
       </c>
       <c r="J2" t="n">
-        <v>0.951256815512</v>
+        <v>0.9190718881478736</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.892929350084</v>
+        <v>-0.9196738121092068</v>
       </c>
       <c r="L2" t="n">
-        <v>33.6058236449</v>
+        <v>33.77014638996533</v>
       </c>
       <c r="M2" t="n">
-        <v>0.174553774256</v>
+        <v>0.1712711779439541</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.396059462633</v>
+        <v>0.3960828540718013</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.347854146545</v>
+        <v>-0.347799448189229</v>
       </c>
     </row>
     <row r="3">
@@ -572,46 +572,46 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.316945782108</v>
+        <v>0.3169457821084706</v>
       </c>
       <c r="E3" t="n">
-        <v>0.316945782108</v>
+        <v>0.3169457821084701</v>
       </c>
       <c r="F3" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181778</v>
       </c>
       <c r="G3" t="n">
-        <v>24.1572075214</v>
+        <v>24.19097325933423</v>
       </c>
       <c r="H3" t="n">
-        <v>7.38296540759</v>
+        <v>7.389447109549408</v>
       </c>
       <c r="I3" t="n">
-        <v>3.31088307464</v>
+        <v>3.313946241024291</v>
       </c>
       <c r="J3" t="n">
-        <v>0.933093906282</v>
+        <v>0.9009265687850273</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8928633309939999</v>
+        <v>-0.9196042978121353</v>
       </c>
       <c r="L3" t="n">
-        <v>33.931915403</v>
+        <v>34.03689804671798</v>
       </c>
       <c r="M3" t="n">
-        <v>0.178273253175</v>
+        <v>0.1711189754816507</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5527136788e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.39608674022</v>
+        <v>0.3961100865498786</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.342267344474</v>
+        <v>-0.3422104291054451</v>
       </c>
     </row>
     <row r="4">
@@ -627,46 +627,46 @@
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.318843874507</v>
+        <v>0.3188438745071276</v>
       </c>
       <c r="E4" t="n">
-        <v>0.318843874507</v>
+        <v>0.3188438745071284</v>
       </c>
       <c r="F4" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181785</v>
       </c>
       <c r="G4" t="n">
-        <v>24.1488581477</v>
+        <v>24.17480479625255</v>
       </c>
       <c r="H4" t="n">
-        <v>7.38021881335</v>
+        <v>7.386653685645744</v>
       </c>
       <c r="I4" t="n">
-        <v>3.31016105411</v>
+        <v>3.313225312102758</v>
       </c>
       <c r="J4" t="n">
-        <v>0.925055207507</v>
+        <v>0.892891610950429</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.892907679052</v>
+        <v>-0.9196499032061957</v>
       </c>
       <c r="L4" t="n">
-        <v>34.1249348281</v>
+        <v>34.1818304814794</v>
       </c>
       <c r="M4" t="n">
-        <v>0.177309584878</v>
+        <v>0.1712231956479534</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4408920985e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.396080413089</v>
+        <v>0.3961037868268742</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.345013938715</v>
+        <v>-0.3450038530091097</v>
       </c>
     </row>
     <row r="5">
@@ -682,46 +682,46 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.318682056158</v>
+        <v>0.3186820561583312</v>
       </c>
       <c r="E5" t="n">
-        <v>0.318682056158</v>
+        <v>0.3186820561583326</v>
       </c>
       <c r="F5" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518179</v>
       </c>
       <c r="G5" t="n">
-        <v>24.0989882885</v>
+        <v>24.12493493709372</v>
       </c>
       <c r="H5" t="n">
-        <v>7.38200158638</v>
+        <v>7.388452739711536</v>
       </c>
       <c r="I5" t="n">
-        <v>3.30794043436</v>
+        <v>3.310995415033759</v>
       </c>
       <c r="J5" t="n">
-        <v>0.925963923801</v>
+        <v>0.8937976843715953</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.892826116059</v>
+        <v>-0.9195685280903253</v>
       </c>
       <c r="L5" t="n">
-        <v>34.1844794408</v>
+        <v>34.30018171102702</v>
       </c>
       <c r="M5" t="n">
-        <v>0.176179585174</v>
+        <v>0.1667088002191865</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6645352591e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.396106247245</v>
+        <v>0.3961295832491882</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.343231165686</v>
+        <v>-0.3432047989433169</v>
       </c>
     </row>
     <row r="6">
@@ -737,46 +737,46 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.324788569149</v>
+        <v>0.3247885691493536</v>
       </c>
       <c r="E6" t="n">
-        <v>0.324788569149</v>
+        <v>0.3247885691493536</v>
       </c>
       <c r="F6" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181782</v>
       </c>
       <c r="G6" t="n">
-        <v>24.1361440089</v>
+        <v>24.1622055393873</v>
       </c>
       <c r="H6" t="n">
-        <v>7.38894067041</v>
+        <v>7.395374448887399</v>
       </c>
       <c r="I6" t="n">
-        <v>3.31309390461</v>
+        <v>3.316159842394165</v>
       </c>
       <c r="J6" t="n">
-        <v>0.900251727676</v>
+        <v>0.8681037914495983</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.892911467066</v>
+        <v>-0.9196541416550547</v>
       </c>
       <c r="L6" t="n">
-        <v>35.0609063555</v>
+        <v>35.18936920788872</v>
       </c>
       <c r="M6" t="n">
-        <v>0.173983546708</v>
+        <v>0.1678990373989942</v>
       </c>
       <c r="N6" t="n">
-        <v>1.11022302463e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.39613591487</v>
+        <v>0.3961592932089457</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.336292081662</v>
+        <v>-0.3362830897674547</v>
       </c>
     </row>
     <row r="7">
@@ -792,46 +792,46 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.322148883938</v>
+        <v>0.3221488839382121</v>
       </c>
       <c r="E7" t="n">
-        <v>0.322148883938</v>
+        <v>0.3221488839382139</v>
       </c>
       <c r="F7" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181793</v>
       </c>
       <c r="G7" t="n">
-        <v>24.0980106339</v>
+        <v>24.1239572825174</v>
       </c>
       <c r="H7" t="n">
-        <v>7.39965836931</v>
+        <v>7.406059881564178</v>
       </c>
       <c r="I7" t="n">
-        <v>3.31647943495</v>
+        <v>3.319552089856698</v>
       </c>
       <c r="J7" t="n">
-        <v>0.911235899758</v>
+        <v>0.879068238992694</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.892862486189</v>
+        <v>-0.9196062467519073</v>
       </c>
       <c r="L7" t="n">
-        <v>34.8185967405</v>
+        <v>34.96419930829309</v>
       </c>
       <c r="M7" t="n">
-        <v>0.17550385135</v>
+        <v>0.169265298792018</v>
       </c>
       <c r="N7" t="n">
-        <v>1.7763568394e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.39614806682</v>
+        <v>0.3961714261227764</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.325574382759</v>
+        <v>-0.3255976570906753</v>
       </c>
     </row>
     <row r="8">
@@ -847,46 +847,46 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.319694642393</v>
+        <v>0.3196946423929882</v>
       </c>
       <c r="E8" t="n">
-        <v>0.319694642393</v>
+        <v>0.3196946423929893</v>
       </c>
       <c r="F8" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181789</v>
       </c>
       <c r="G8" t="n">
-        <v>24.1153728223</v>
+        <v>24.16712929075134</v>
       </c>
       <c r="H8" t="n">
-        <v>7.38113919389</v>
+        <v>7.387608825737398</v>
       </c>
       <c r="I8" t="n">
-        <v>3.30686250751</v>
+        <v>3.309923866255608</v>
       </c>
       <c r="J8" t="n">
-        <v>0.921557470914</v>
+        <v>0.8893962698443193</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.892928848659</v>
+        <v>-0.919671010074819</v>
       </c>
       <c r="L8" t="n">
-        <v>34.2061392588</v>
+        <v>34.38365899348981</v>
       </c>
       <c r="M8" t="n">
-        <v>0.175539920465</v>
+        <v>0.165668297531839</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6645352591e-15</v>
+        <v>4.440892098500626e-15</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.396086663681</v>
+        <v>0.3961100001818751</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.344093558179</v>
+        <v>-0.3440487129174556</v>
       </c>
     </row>
     <row r="9">
@@ -902,46 +902,46 @@
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0.32045441829</v>
+        <v>0.3204544182904502</v>
       </c>
       <c r="E9" t="n">
-        <v>0.32045441829</v>
+        <v>0.3204544182904522</v>
       </c>
       <c r="F9" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181793</v>
       </c>
       <c r="G9" t="n">
-        <v>24.1080460594</v>
+        <v>24.13399270798379</v>
       </c>
       <c r="H9" t="n">
-        <v>7.38832190322</v>
+        <v>7.394739138692504</v>
       </c>
       <c r="I9" t="n">
-        <v>3.31706953946</v>
+        <v>3.320125160819414</v>
       </c>
       <c r="J9" t="n">
-        <v>0.918220736419</v>
+        <v>0.8860574672832825</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.892973051907</v>
+        <v>-0.9197166467748235</v>
       </c>
       <c r="L9" t="n">
-        <v>34.3409818071</v>
+        <v>34.47187871411387</v>
       </c>
       <c r="M9" t="n">
-        <v>0.177779786846</v>
+        <v>0.1717913266535264</v>
       </c>
       <c r="N9" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.396110100819</v>
+        <v>0.3961334586265031</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.336910848844</v>
+        <v>-0.3369183999623493</v>
       </c>
     </row>
     <row r="10">
@@ -957,46 +957,46 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>0.307833923462</v>
+        <v>0.3078339234623259</v>
       </c>
       <c r="E10" t="n">
-        <v>0.307833923462</v>
+        <v>0.3078339234623271</v>
       </c>
       <c r="F10" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181789</v>
       </c>
       <c r="G10" t="n">
-        <v>24.1110281701</v>
+        <v>24.15508043111402</v>
       </c>
       <c r="H10" t="n">
-        <v>7.38322589866</v>
+        <v>7.389633965757524</v>
       </c>
       <c r="I10" t="n">
-        <v>3.31155990562</v>
+        <v>3.314623066481622</v>
       </c>
       <c r="J10" t="n">
-        <v>0.971396983411</v>
+        <v>0.9391991762847892</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.892858604802</v>
+        <v>-0.9196019940707322</v>
       </c>
       <c r="L10" t="n">
-        <v>33.2850951941</v>
+        <v>33.46375848854793</v>
       </c>
       <c r="M10" t="n">
-        <v>0.173820217357</v>
+        <v>0.1697412647769435</v>
       </c>
       <c r="N10" t="n">
-        <v>6.66133814775e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.396072557528</v>
+        <v>0.3960960009317922</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.342006853407</v>
+        <v>-0.3420235728973298</v>
       </c>
     </row>
     <row r="11">
@@ -1012,46 +1012,46 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>0.311370722843</v>
+        <v>0.3113707228428236</v>
       </c>
       <c r="E11" t="n">
-        <v>0.311370722843</v>
+        <v>0.3113707228428246</v>
       </c>
       <c r="F11" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G11" t="n">
-        <v>24.1311496848</v>
+        <v>24.15721121528662</v>
       </c>
       <c r="H11" t="n">
-        <v>7.38239799053</v>
+        <v>7.388847522286632</v>
       </c>
       <c r="I11" t="n">
-        <v>3.30960302654</v>
+        <v>3.31266644844364</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9560645178329999</v>
+        <v>0.9238696115925217</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.892995118929</v>
+        <v>-0.9197383437998501</v>
       </c>
       <c r="L11" t="n">
-        <v>33.4420615884</v>
+        <v>33.61782676318632</v>
       </c>
       <c r="M11" t="n">
-        <v>0.177207302314</v>
+        <v>0.1710281128948865</v>
       </c>
       <c r="N11" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.396062184567</v>
+        <v>0.3960855602596405</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.342834761541</v>
+        <v>-0.3428100163682215</v>
       </c>
     </row>
     <row r="12">
@@ -1067,46 +1067,46 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.33313583476</v>
+        <v>0.3331358347595158</v>
       </c>
       <c r="E12" t="n">
-        <v>0.33313583476</v>
+        <v>0.3331358347595151</v>
       </c>
       <c r="F12" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181778</v>
       </c>
       <c r="G12" t="n">
-        <v>24.1269699471</v>
+        <v>24.18654550491827</v>
       </c>
       <c r="H12" t="n">
-        <v>7.39880352516</v>
+        <v>7.405261329109916</v>
       </c>
       <c r="I12" t="n">
-        <v>3.31886552295</v>
+        <v>3.321934263654795</v>
       </c>
       <c r="J12" t="n">
-        <v>0.865368869526</v>
+        <v>0.8332285581343349</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.892771969627</v>
+        <v>-0.9195161724023164</v>
       </c>
       <c r="L12" t="n">
-        <v>35.555066813</v>
+        <v>35.71938955809063</v>
       </c>
       <c r="M12" t="n">
-        <v>0.172908918837</v>
+        <v>0.1691910671952917</v>
       </c>
       <c r="N12" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.396229421026</v>
+        <v>0.3962528402113095</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.326429226907</v>
+        <v>-0.3263962095449378</v>
       </c>
     </row>
     <row r="13">
@@ -1122,46 +1122,46 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.342875746845</v>
+        <v>0.3428757468448507</v>
       </c>
       <c r="E13" t="n">
-        <v>0.342875746845</v>
+        <v>0.3428757468448503</v>
       </c>
       <c r="F13" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181779</v>
       </c>
       <c r="G13" t="n">
-        <v>24.191783448</v>
+        <v>24.22554918597035</v>
       </c>
       <c r="H13" t="n">
-        <v>7.41075143284</v>
+        <v>7.417226653623403</v>
       </c>
       <c r="I13" t="n">
-        <v>3.33082199669</v>
+        <v>3.333892202358642</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8246914599389999</v>
+        <v>0.7925817557117424</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.892675191338</v>
+        <v>-0.9194170771165664</v>
       </c>
       <c r="L13" t="n">
-        <v>36.459269197</v>
+        <v>36.55143575704321</v>
       </c>
       <c r="M13" t="n">
-        <v>0.177207326529</v>
+        <v>0.1694092731658617</v>
       </c>
       <c r="N13" t="n">
-        <v>1.33226762955e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.396287931564</v>
+        <v>0.3963112627602794</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.314481319231</v>
+        <v>-0.3144308850314506</v>
       </c>
     </row>
     <row r="14">
@@ -1177,46 +1177,46 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>0.340092043815</v>
+        <v>0.3400920438150287</v>
       </c>
       <c r="E14" t="n">
-        <v>0.340092043815</v>
+        <v>0.3400920438150288</v>
       </c>
       <c r="F14" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181782</v>
       </c>
       <c r="G14" t="n">
-        <v>24.1626542894</v>
+        <v>24.18860093802288</v>
       </c>
       <c r="H14" t="n">
-        <v>7.40228291293</v>
+        <v>7.408731740118608</v>
       </c>
       <c r="I14" t="n">
-        <v>3.32744260703</v>
+        <v>3.33051496504743</v>
       </c>
       <c r="J14" t="n">
-        <v>0.836195535871</v>
+        <v>0.8040755062710263</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.892731605595</v>
+        <v>-0.9194741819883088</v>
       </c>
       <c r="L14" t="n">
-        <v>36.1922675631</v>
+        <v>36.26287267122908</v>
       </c>
       <c r="M14" t="n">
-        <v>0.178153346718</v>
+        <v>0.1715660792078939</v>
       </c>
       <c r="N14" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.39625049009</v>
+        <v>0.3962738733331623</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.322949839135</v>
+        <v>-0.3229257985362457</v>
       </c>
     </row>
     <row r="15">
@@ -1232,46 +1232,46 @@
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>0.336001564417</v>
+        <v>0.3360015644172485</v>
       </c>
       <c r="E15" t="n">
-        <v>0.336001564417</v>
+        <v>0.33600156441725</v>
       </c>
       <c r="F15" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181791</v>
       </c>
       <c r="G15" t="n">
-        <v>24.0250919402</v>
+        <v>24.05103858881175</v>
       </c>
       <c r="H15" t="n">
-        <v>7.40107192434</v>
+        <v>7.407487587009496</v>
       </c>
       <c r="I15" t="n">
-        <v>3.31843194436</v>
+        <v>3.321499502254963</v>
       </c>
       <c r="J15" t="n">
-        <v>0.853441470677</v>
+        <v>0.8213080617638121</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.8926781271000001</v>
+        <v>-0.9194210352187144</v>
       </c>
       <c r="L15" t="n">
-        <v>35.9273986866</v>
+        <v>36.04310095675324</v>
       </c>
       <c r="M15" t="n">
-        <v>0.173098610891</v>
+        <v>0.1641802213562155</v>
       </c>
       <c r="N15" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.396245949163</v>
+        <v>0.3962692977541382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.324160827729</v>
+        <v>-0.3241699516453576</v>
       </c>
     </row>
     <row r="16">
@@ -1287,46 +1287,46 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>0.352283294327</v>
+        <v>0.3522832943266541</v>
       </c>
       <c r="E16" t="n">
-        <v>0.352283294327</v>
+        <v>0.3522832943266539</v>
       </c>
       <c r="F16" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181781</v>
       </c>
       <c r="G16" t="n">
-        <v>24.1990395624</v>
+        <v>24.25091091277822</v>
       </c>
       <c r="H16" t="n">
-        <v>7.41579664363</v>
+        <v>7.422250978961762</v>
       </c>
       <c r="I16" t="n">
-        <v>3.32758248262</v>
+        <v>3.330659475383538</v>
       </c>
       <c r="J16" t="n">
-        <v>0.785219882387</v>
+        <v>0.7531277524771822</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.892741327313</v>
+        <v>-0.9194852631023078</v>
       </c>
       <c r="L16" t="n">
-        <v>37.5202589633</v>
+        <v>37.62314514969761</v>
       </c>
       <c r="M16" t="n">
-        <v>0.173931767183</v>
+        <v>0.1644099730249831</v>
       </c>
       <c r="N16" t="n">
-        <v>1.33226762955e-15</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.396335612983</v>
+        <v>0.3963589957500777</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.309436108441</v>
+        <v>-0.3094065596930911</v>
       </c>
     </row>
     <row r="17">
@@ -1342,46 +1342,46 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.349037760783</v>
+        <v>0.3490377607830287</v>
       </c>
       <c r="E17" t="n">
-        <v>0.349037760783</v>
+        <v>0.3490377607830298</v>
       </c>
       <c r="F17" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G17" t="n">
-        <v>24.1556871892</v>
+        <v>24.18163383778463</v>
       </c>
       <c r="H17" t="n">
-        <v>7.42455361284</v>
+        <v>7.430962237989299</v>
       </c>
       <c r="I17" t="n">
-        <v>3.33403457059</v>
+        <v>3.337114992538535</v>
       </c>
       <c r="J17" t="n">
-        <v>0.798624754915</v>
+        <v>0.7665078970786855</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.892717773757</v>
+        <v>-0.9194640031304706</v>
       </c>
       <c r="L17" t="n">
-        <v>37.4276482271</v>
+        <v>37.57325079488052</v>
       </c>
       <c r="M17" t="n">
-        <v>0.175100682924</v>
+        <v>0.1674266616451076</v>
       </c>
       <c r="N17" t="n">
-        <v>1.7763568394e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.396353963449</v>
+        <v>0.3963773390989276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.300679139231</v>
+        <v>-0.3006953006655548</v>
       </c>
     </row>
     <row r="18">
@@ -1397,46 +1397,46 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>0.347487805794</v>
+        <v>0.3474878057938253</v>
       </c>
       <c r="E18" t="n">
-        <v>0.347487805794</v>
+        <v>0.3474878057938269</v>
       </c>
       <c r="F18" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181791</v>
       </c>
       <c r="G18" t="n">
-        <v>24.1348673209</v>
+        <v>24.18662378937711</v>
       </c>
       <c r="H18" t="n">
-        <v>7.40978107831</v>
+        <v>7.416232027313856</v>
       </c>
       <c r="I18" t="n">
-        <v>3.32135954569</v>
+        <v>3.324431358180897</v>
       </c>
       <c r="J18" t="n">
-        <v>0.805317443964</v>
+        <v>0.7732119647656657</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.892753949869</v>
+        <v>-0.9194972859137075</v>
       </c>
       <c r="L18" t="n">
-        <v>36.9151275121</v>
+        <v>37.09264724680356</v>
       </c>
       <c r="M18" t="n">
-        <v>0.17526062149</v>
+        <v>0.1630920985349905</v>
       </c>
       <c r="N18" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.396276820644</v>
+        <v>0.3963001520138918</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.315451673754</v>
+        <v>-0.3154255113409974</v>
       </c>
     </row>
     <row r="19">
@@ -1452,46 +1452,46 @@
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>0.344927067991</v>
+        <v>0.344927067990722</v>
       </c>
       <c r="E19" t="n">
-        <v>0.344927067991</v>
+        <v>0.3449270679907244</v>
       </c>
       <c r="F19" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181796</v>
       </c>
       <c r="G19" t="n">
-        <v>24.1309547191</v>
+        <v>24.15690136770439</v>
       </c>
       <c r="H19" t="n">
-        <v>7.41575142912</v>
+        <v>7.422186244227469</v>
       </c>
       <c r="I19" t="n">
-        <v>3.33391402632</v>
+        <v>3.336981756605733</v>
       </c>
       <c r="J19" t="n">
-        <v>0.815823651943</v>
+        <v>0.7837083754804242</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.892818033464</v>
+        <v>-0.9195629913739066</v>
       </c>
       <c r="L19" t="n">
-        <v>36.7575370256</v>
+        <v>36.86285726661488</v>
       </c>
       <c r="M19" t="n">
-        <v>0.176038859661</v>
+        <v>0.1671836268348764</v>
       </c>
       <c r="N19" t="n">
-        <v>2.6645352591e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.396298801498</v>
+        <v>0.3963221764985798</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.30948132295</v>
+        <v>-0.3094712944273841</v>
       </c>
     </row>
     <row r="20">
@@ -1507,46 +1507,46 @@
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>0.330051286012</v>
+        <v>0.3300512860121974</v>
       </c>
       <c r="E20" t="n">
-        <v>0.330051286012</v>
+        <v>0.3300512860121994</v>
       </c>
       <c r="F20" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181793</v>
       </c>
       <c r="G20" t="n">
-        <v>24.1706316605</v>
+        <v>24.2146839214783</v>
       </c>
       <c r="H20" t="n">
-        <v>7.40576365988</v>
+        <v>7.412161998737133</v>
       </c>
       <c r="I20" t="n">
-        <v>3.32617352028</v>
+        <v>3.329242280743278</v>
       </c>
       <c r="J20" t="n">
-        <v>0.878493340885</v>
+        <v>0.8463386798912615</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.892703111003</v>
+        <v>-0.9194470389412843</v>
       </c>
       <c r="L20" t="n">
-        <v>35.5038971104</v>
+        <v>35.68256040486257</v>
       </c>
       <c r="M20" t="n">
-        <v>0.172186800061</v>
+        <v>0.168073330255628</v>
       </c>
       <c r="N20" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.396243329451</v>
+        <v>0.3962667922201344</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.319469092187</v>
+        <v>-0.3194955399177202</v>
       </c>
     </row>
     <row r="21">
@@ -1565,43 +1565,43 @@
         <v>0.337710559234</v>
       </c>
       <c r="E21" t="n">
-        <v>0.337710559234</v>
+        <v>0.3377105592340021</v>
       </c>
       <c r="F21" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181796</v>
       </c>
       <c r="G21" t="n">
-        <v>24.143497491</v>
+        <v>24.16955902148259</v>
       </c>
       <c r="H21" t="n">
-        <v>7.40874111546</v>
+        <v>7.415188770263257</v>
       </c>
       <c r="I21" t="n">
-        <v>3.32691711458</v>
+        <v>3.329991805408827</v>
       </c>
       <c r="J21" t="n">
-        <v>0.845863885532</v>
+        <v>0.813722723267234</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.892815740627</v>
+        <v>-0.9195603442305006</v>
       </c>
       <c r="L21" t="n">
-        <v>36.1605807826</v>
+        <v>36.33634595732971</v>
       </c>
       <c r="M21" t="n">
-        <v>0.173456192669</v>
+        <v>0.1671002222189779</v>
       </c>
       <c r="N21" t="n">
-        <v>1.11022302463e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.396262385939</v>
+        <v>0.3962857605914434</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.316491636608</v>
+        <v>-0.3164687683915961</v>
       </c>
     </row>
     <row r="22">
@@ -1617,46 +1617,46 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.355503830803</v>
+        <v>0.3555038308034971</v>
       </c>
       <c r="E22" t="n">
-        <v>0.355503830803</v>
+        <v>0.3555038308034962</v>
       </c>
       <c r="F22" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181778</v>
       </c>
       <c r="G22" t="n">
-        <v>24.1262765501</v>
+        <v>24.18585210791629</v>
       </c>
       <c r="H22" t="n">
-        <v>7.42783684589</v>
+        <v>7.434284534779505</v>
       </c>
       <c r="I22" t="n">
-        <v>3.33884184039</v>
+        <v>3.341915637875206</v>
       </c>
       <c r="J22" t="n">
-        <v>0.771768913134</v>
+        <v>0.7396754375606406</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.892631869525</v>
+        <v>-0.9193761154238691</v>
       </c>
       <c r="L22" t="n">
-        <v>37.7222522163</v>
+        <v>37.86099829535712</v>
       </c>
       <c r="M22" t="n">
-        <v>0.17213989648</v>
+        <v>0.1670790168343728</v>
       </c>
       <c r="N22" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.396406583932</v>
+        <v>0.396429983711069</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.297395906182</v>
+        <v>-0.2973730038753484</v>
       </c>
     </row>
     <row r="23">
@@ -1672,46 +1672,46 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.364570955609</v>
+        <v>0.3645709556087854</v>
       </c>
       <c r="E23" t="n">
-        <v>0.364570955609</v>
+        <v>0.3645709556087852</v>
       </c>
       <c r="F23" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181778</v>
       </c>
       <c r="G23" t="n">
-        <v>24.251382607</v>
+        <v>24.27744413754174</v>
       </c>
       <c r="H23" t="n">
-        <v>7.4270521304</v>
+        <v>7.433551744331024</v>
       </c>
       <c r="I23" t="n">
-        <v>3.34001964905</v>
+        <v>3.343097438016613</v>
       </c>
       <c r="J23" t="n">
-        <v>0.733940287332</v>
+        <v>0.7018748726568125</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8925222305029999</v>
+        <v>-0.919264954997008</v>
       </c>
       <c r="L23" t="n">
-        <v>38.7019584838</v>
+        <v>38.78745086085219</v>
       </c>
       <c r="M23" t="n">
-        <v>0.17471279671</v>
+        <v>0.1671192956101454</v>
       </c>
       <c r="N23" t="n">
-        <v>1.7763568394e-15</v>
+        <v>4.440892098500626e-15</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.396447945361</v>
+        <v>0.396471293789979</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.298180621672</v>
+        <v>-0.2981057943238294</v>
       </c>
     </row>
     <row r="24">
@@ -1727,46 +1727,46 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.354479238596</v>
+        <v>0.3544792385964288</v>
       </c>
       <c r="E24" t="n">
-        <v>0.354479238596</v>
+        <v>0.3544792385964294</v>
       </c>
       <c r="F24" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181784</v>
       </c>
       <c r="G24" t="n">
-        <v>24.200594548</v>
+        <v>24.22654119657493</v>
       </c>
       <c r="H24" t="n">
-        <v>7.41891676864</v>
+        <v>7.425368416137814</v>
       </c>
       <c r="I24" t="n">
-        <v>3.33538004457</v>
+        <v>3.338457811895657</v>
       </c>
       <c r="J24" t="n">
-        <v>0.776034791657</v>
+        <v>0.7439416388367402</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.89261104531</v>
+        <v>-0.9193544482802667</v>
       </c>
       <c r="L24" t="n">
-        <v>37.6683347719</v>
+        <v>37.6889301078393</v>
       </c>
       <c r="M24" t="n">
-        <v>0.175746594847</v>
+        <v>0.1692938411742145</v>
       </c>
       <c r="N24" t="n">
-        <v>6.66133814775e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.396358285509</v>
+        <v>0.3963816691043378</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.306315983427</v>
+        <v>-0.3062891225170397</v>
       </c>
     </row>
     <row r="25">
@@ -1782,46 +1782,46 @@
         <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.35421983513</v>
+        <v>0.3542198351301206</v>
       </c>
       <c r="E25" t="n">
-        <v>0.35421983513</v>
+        <v>0.3542198351301221</v>
       </c>
       <c r="F25" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181791</v>
       </c>
       <c r="G25" t="n">
-        <v>24.0582555956</v>
+        <v>24.08420224419627</v>
       </c>
       <c r="H25" t="n">
-        <v>7.4251965103</v>
+        <v>7.43161822983638</v>
       </c>
       <c r="I25" t="n">
-        <v>3.33673233541</v>
+        <v>3.33980876916118</v>
       </c>
       <c r="J25" t="n">
-        <v>0.777437677566</v>
+        <v>0.7453418420570074</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.892541043303</v>
+        <v>-0.9192852415180237</v>
       </c>
       <c r="L25" t="n">
-        <v>37.8783599169</v>
+        <v>37.98005923494616</v>
       </c>
       <c r="M25" t="n">
-        <v>0.172395498318</v>
+        <v>0.1628470532499886</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6645352591e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.396407410092</v>
+        <v>0.3964307685983595</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.300036241769</v>
+        <v>-0.3000393088184738</v>
       </c>
     </row>
     <row r="26">
@@ -1837,46 +1837,46 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.367750657552</v>
+        <v>0.3677506575521403</v>
       </c>
       <c r="E26" t="n">
-        <v>0.367750657552</v>
+        <v>0.3677506575521393</v>
       </c>
       <c r="F26" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181775</v>
       </c>
       <c r="G26" t="n">
-        <v>24.2190386283</v>
+        <v>24.27090997867995</v>
       </c>
       <c r="H26" t="n">
-        <v>7.43631307703</v>
+        <v>7.442771493467507</v>
       </c>
       <c r="I26" t="n">
-        <v>3.34032954159</v>
+        <v>3.34341716501694</v>
       </c>
       <c r="J26" t="n">
-        <v>0.720516036128</v>
+        <v>0.6884516840961195</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.89260210515</v>
+        <v>-0.9193465170605106</v>
       </c>
       <c r="L26" t="n">
-        <v>39.1105308162</v>
+        <v>39.31426859762864</v>
       </c>
       <c r="M26" t="n">
-        <v>0.173724662062</v>
+        <v>0.1634064065003354</v>
       </c>
       <c r="N26" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.396473568536</v>
+        <v>0.3964969645898346</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.288919675037</v>
+        <v>-0.2888860451873461</v>
       </c>
     </row>
     <row r="27">
@@ -1892,46 +1892,46 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.367840792106</v>
+        <v>0.367840792105557</v>
       </c>
       <c r="E27" t="n">
-        <v>0.367840792106</v>
+        <v>0.3678407921055577</v>
       </c>
       <c r="F27" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G27" t="n">
-        <v>24.1621164842</v>
+        <v>24.18806313281388</v>
       </c>
       <c r="H27" t="n">
-        <v>7.4474098783</v>
+        <v>7.453801952279574</v>
       </c>
       <c r="I27" t="n">
-        <v>3.34477265598</v>
+        <v>3.347860456394535</v>
       </c>
       <c r="J27" t="n">
-        <v>0.720046274587</v>
+        <v>0.6879676939768963</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.892562128168</v>
+        <v>-0.9193089747315072</v>
       </c>
       <c r="L27" t="n">
-        <v>39.2900111898</v>
+        <v>39.43561375757665</v>
       </c>
       <c r="M27" t="n">
-        <v>0.174186669582</v>
+        <v>0.1654217521195905</v>
       </c>
       <c r="N27" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.554312234475219e-15</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.396505452672</v>
+        <v>0.3965288231390951</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.27782287377</v>
+        <v>-0.2778555863752796</v>
       </c>
     </row>
     <row r="28">
@@ -1947,46 +1947,46 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.360907001937</v>
+        <v>0.3609070019373153</v>
       </c>
       <c r="E28" t="n">
-        <v>0.360907001937</v>
+        <v>0.360907001937317</v>
       </c>
       <c r="F28" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181792</v>
       </c>
       <c r="G28" t="n">
-        <v>24.1773893474</v>
+        <v>24.2291458159057</v>
       </c>
       <c r="H28" t="n">
-        <v>7.42235440516</v>
+        <v>7.428803786053812</v>
       </c>
       <c r="I28" t="n">
-        <v>3.32836433723</v>
+        <v>3.331440191108365</v>
       </c>
       <c r="J28" t="n">
-        <v>0.749175384921</v>
+        <v>0.7170965777197278</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.892652037508</v>
+        <v>-0.9193966762769977</v>
       </c>
       <c r="L28" t="n">
-        <v>38.2674698203</v>
+        <v>38.44498955494296</v>
       </c>
       <c r="M28" t="n">
-        <v>0.171169734986</v>
+        <v>0.15979710252744</v>
       </c>
       <c r="N28" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0.396378849849</v>
+        <v>0.396402188071548</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.302878346906</v>
+        <v>-0.3028537526010417</v>
       </c>
     </row>
     <row r="29">
@@ -2002,46 +2002,46 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.366613343384</v>
+        <v>0.3666133433837184</v>
       </c>
       <c r="E29" t="n">
-        <v>0.366613343384</v>
+        <v>0.3666133433837214</v>
       </c>
       <c r="F29" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181799</v>
       </c>
       <c r="G29" t="n">
-        <v>24.1557595113</v>
+        <v>24.2075159797203</v>
       </c>
       <c r="H29" t="n">
-        <v>7.44167046662</v>
+        <v>7.448118684755024</v>
       </c>
       <c r="I29" t="n">
-        <v>3.34767304345</v>
+        <v>3.350753676368942</v>
       </c>
       <c r="J29" t="n">
-        <v>0.725101692291</v>
+        <v>0.6930275351361269</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.892666944656</v>
+        <v>-0.9194126558491054</v>
       </c>
       <c r="L29" t="n">
-        <v>38.8317554845</v>
+        <v>38.98467361851583</v>
       </c>
       <c r="M29" t="n">
-        <v>0.174229330251</v>
+        <v>0.1636927134381629</v>
       </c>
       <c r="N29" t="n">
-        <v>2.22044604925e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0.396475224085</v>
+        <v>0.3964985980674829</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.283562285451</v>
+        <v>-0.2835388538998291</v>
       </c>
     </row>
     <row r="30">
@@ -2057,46 +2057,46 @@
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>0.348273772199</v>
+        <v>0.3482737721990727</v>
       </c>
       <c r="E30" t="n">
-        <v>0.348273772199</v>
+        <v>0.3482737721990753</v>
       </c>
       <c r="F30" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181798</v>
       </c>
       <c r="G30" t="n">
-        <v>24.1785407261</v>
+        <v>24.22259298712363</v>
       </c>
       <c r="H30" t="n">
-        <v>7.42520161594</v>
+        <v>7.431585205860689</v>
       </c>
       <c r="I30" t="n">
-        <v>3.33640224676</v>
+        <v>3.339477545234032</v>
       </c>
       <c r="J30" t="n">
-        <v>0.802269751517</v>
+        <v>0.7701530740588922</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.892561017182</v>
+        <v>-0.9193053373426452</v>
       </c>
       <c r="L30" t="n">
-        <v>37.3775230653</v>
+        <v>37.58488176974323</v>
       </c>
       <c r="M30" t="n">
-        <v>0.170538320949</v>
+        <v>0.1649175390930206</v>
       </c>
       <c r="N30" t="n">
-        <v>1.7763568394e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0.396388256887</v>
+        <v>0.3964116979707315</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.300031136129</v>
+        <v>-0.3000723327941648</v>
       </c>
     </row>
     <row r="31">
@@ -2112,46 +2112,46 @@
         <v>9</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3564737312</v>
+        <v>0.3564737311999185</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3564737312</v>
+        <v>0.3564737311999208</v>
       </c>
       <c r="F31" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181797</v>
       </c>
       <c r="G31" t="n">
-        <v>24.221895641</v>
+        <v>24.24795717150481</v>
       </c>
       <c r="H31" t="n">
-        <v>7.43361025808</v>
+        <v>7.440049177959023</v>
       </c>
       <c r="I31" t="n">
-        <v>3.3391731652</v>
+        <v>3.342257763918636</v>
       </c>
       <c r="J31" t="n">
-        <v>0.767351320868</v>
+        <v>0.7352463108238499</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.8926929134179999</v>
+        <v>-0.9194381170877813</v>
       </c>
       <c r="L31" t="n">
-        <v>37.9914896799</v>
+        <v>38.18927608166568</v>
       </c>
       <c r="M31" t="n">
-        <v>0.172140148107</v>
+        <v>0.1640605220725559</v>
       </c>
       <c r="N31" t="n">
-        <v>1.7763568394e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0.396411938612</v>
+        <v>0.3964353129798579</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.291622493991</v>
+        <v>-0.2916083606958306</v>
       </c>
     </row>
     <row r="32">
@@ -2167,46 +2167,46 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.384581841324</v>
+        <v>0.3845818413242594</v>
       </c>
       <c r="E32" t="n">
-        <v>0.384581841324</v>
+        <v>0.3845818413242585</v>
       </c>
       <c r="F32" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181777</v>
       </c>
       <c r="G32" t="n">
-        <v>24.158932141</v>
+        <v>24.218507698826</v>
       </c>
       <c r="H32" t="n">
-        <v>7.46351904264</v>
+        <v>7.469981386630669</v>
       </c>
       <c r="I32" t="n">
-        <v>3.36461154769</v>
+        <v>3.367696862021085</v>
       </c>
       <c r="J32" t="n">
-        <v>0.650263644407</v>
+        <v>0.6182303881742343</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.892395007472</v>
+        <v>-0.9191404186824156</v>
       </c>
       <c r="L32" t="n">
-        <v>40.64669538</v>
+        <v>40.76322250742511</v>
       </c>
       <c r="M32" t="n">
-        <v>0.168470073577</v>
+        <v>0.1618653070861328</v>
       </c>
       <c r="N32" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.396656074546</v>
+        <v>0.3966794550480561</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.261713709433</v>
+        <v>-0.2616761520241839</v>
       </c>
     </row>
     <row r="33">
@@ -2222,46 +2222,46 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.394329620577</v>
+        <v>0.3943296205770965</v>
       </c>
       <c r="E33" t="n">
-        <v>0.394329620577</v>
+        <v>0.3943296205770964</v>
       </c>
       <c r="F33" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518178</v>
       </c>
       <c r="G33" t="n">
-        <v>24.3200335224</v>
+        <v>24.34609505293938</v>
       </c>
       <c r="H33" t="n">
-        <v>7.45920611038</v>
+        <v>7.465724076941441</v>
       </c>
       <c r="I33" t="n">
-        <v>3.36370794043</v>
+        <v>3.366789792315318</v>
       </c>
       <c r="J33" t="n">
-        <v>0.60956729262</v>
+        <v>0.5775641373231539</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.892291859469</v>
+        <v>-0.9190355598854762</v>
       </c>
       <c r="L33" t="n">
-        <v>41.5201967817</v>
+        <v>41.60568915879023</v>
       </c>
       <c r="M33" t="n">
-        <v>0.171683172813</v>
+        <v>0.1629613227034993</v>
       </c>
       <c r="N33" t="n">
-        <v>2.22044604925e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.396678219831</v>
+        <v>0.3967015539659735</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.266026641692</v>
+        <v>-0.2659334617134119</v>
       </c>
     </row>
     <row r="34">
@@ -2277,46 +2277,46 @@
         <v>2</v>
       </c>
       <c r="D34" t="n">
-        <v>0.387081113315</v>
+        <v>0.3870811133145977</v>
       </c>
       <c r="E34" t="n">
-        <v>0.387081113315</v>
+        <v>0.3870811133145978</v>
       </c>
       <c r="F34" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181781</v>
       </c>
       <c r="G34" t="n">
-        <v>24.198579427</v>
+        <v>24.22452607558579</v>
       </c>
       <c r="H34" t="n">
-        <v>7.46193437721</v>
+        <v>7.468364248894694</v>
       </c>
       <c r="I34" t="n">
-        <v>3.36506606477</v>
+        <v>3.368151644210503</v>
       </c>
       <c r="J34" t="n">
-        <v>0.63971916981</v>
+        <v>0.6076928797533305</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.89237529902</v>
+        <v>-0.9191197582146051</v>
       </c>
       <c r="L34" t="n">
-        <v>40.9077708471</v>
+        <v>40.92836618305719</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1721276138</v>
+        <v>0.1644211616561329</v>
       </c>
       <c r="N34" t="n">
-        <v>1.33226762955e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0.396642949714</v>
+        <v>0.3966663032342301</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.263298374858</v>
+        <v>-0.263293289760159</v>
       </c>
     </row>
     <row r="35">
@@ -2332,46 +2332,46 @@
         <v>3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.380060740772</v>
+        <v>0.380060740771737</v>
       </c>
       <c r="E35" t="n">
-        <v>0.380060740772</v>
+        <v>0.380060740771739</v>
       </c>
       <c r="F35" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181794</v>
       </c>
       <c r="G35" t="n">
-        <v>24.0787787845</v>
+        <v>24.1047254331142</v>
       </c>
       <c r="H35" t="n">
-        <v>7.4533645636</v>
+        <v>7.459773684470242</v>
       </c>
       <c r="I35" t="n">
-        <v>3.35530870943</v>
+        <v>3.358391247895938</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6693299329970001</v>
+        <v>0.6372860324967411</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.892397786964</v>
+        <v>-0.9191434523924681</v>
       </c>
       <c r="L35" t="n">
-        <v>40.4434603916</v>
+        <v>40.53848552667824</v>
       </c>
       <c r="M35" t="n">
-        <v>0.173003688518</v>
+        <v>0.1602020185483113</v>
       </c>
       <c r="N35" t="n">
-        <v>4.4408920985e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.396604093479</v>
+        <v>0.3966274299654491</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.271868188473</v>
+        <v>-0.2718838541846118</v>
       </c>
     </row>
     <row r="36">
@@ -2387,46 +2387,46 @@
         <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>0.396051703307</v>
+        <v>0.3960517033065432</v>
       </c>
       <c r="E36" t="n">
-        <v>0.396051703307</v>
+        <v>0.3960517033065423</v>
       </c>
       <c r="F36" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181775</v>
       </c>
       <c r="G36" t="n">
-        <v>24.2390711761</v>
+        <v>24.29094252647276</v>
       </c>
       <c r="H36" t="n">
-        <v>7.46915680081</v>
+        <v>7.475582883550614</v>
       </c>
       <c r="I36" t="n">
-        <v>3.36284382654</v>
+        <v>3.365934808087256</v>
       </c>
       <c r="J36" t="n">
-        <v>0.602122219258</v>
+        <v>0.5701144167552405</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.892447394398</v>
+        <v>-0.919193438353461</v>
       </c>
       <c r="L36" t="n">
-        <v>41.8794083151</v>
+        <v>42.04692009606281</v>
       </c>
       <c r="M36" t="n">
-        <v>0.174544324486</v>
+        <v>0.1603498519731223</v>
       </c>
       <c r="N36" t="n">
-        <v>1.33226762955e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.396704063854</v>
+        <v>0.39672742322188</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.256075951258</v>
+        <v>-0.2560746551042392</v>
       </c>
     </row>
     <row r="37">
@@ -2442,46 +2442,46 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>0.391783504774</v>
+        <v>0.3917835047742986</v>
       </c>
       <c r="E37" t="n">
-        <v>0.391783504774</v>
+        <v>0.3917835047742989</v>
       </c>
       <c r="F37" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181784</v>
       </c>
       <c r="G37" t="n">
-        <v>24.2194935915</v>
+        <v>24.2454402400713</v>
       </c>
       <c r="H37" t="n">
-        <v>7.47314771152</v>
+        <v>7.479549963988891</v>
       </c>
       <c r="I37" t="n">
-        <v>3.35876290802</v>
+        <v>3.361864974963823</v>
       </c>
       <c r="J37" t="n">
-        <v>0.619916618742</v>
+        <v>0.5878837690353141</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.892368472456</v>
+        <v>-0.9191173651048745</v>
       </c>
       <c r="L37" t="n">
-        <v>41.6474756805</v>
+        <v>41.79307824829658</v>
       </c>
       <c r="M37" t="n">
-        <v>0.171743379097</v>
+        <v>0.163076032507914</v>
       </c>
       <c r="N37" t="n">
-        <v>4.4408920985e-16</v>
+        <v>4.440892098500626e-15</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.396686669787</v>
+        <v>0.3967100492601354</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.252085040546</v>
+        <v>-0.2521075746659625</v>
       </c>
     </row>
     <row r="38">
@@ -2497,46 +2497,46 @@
         <v>6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.38255195744</v>
+        <v>0.3825519574399548</v>
       </c>
       <c r="E38" t="n">
-        <v>0.38255195744</v>
+        <v>0.3825519574399552</v>
       </c>
       <c r="F38" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181783</v>
       </c>
       <c r="G38" t="n">
-        <v>24.177117025</v>
+        <v>24.22887349350936</v>
       </c>
       <c r="H38" t="n">
-        <v>7.44635788938</v>
+        <v>7.452791536559948</v>
       </c>
       <c r="I38" t="n">
-        <v>3.34369745613</v>
+        <v>3.346773483439156</v>
       </c>
       <c r="J38" t="n">
-        <v>0.658640282326</v>
+        <v>0.6266005218877578</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.892452356189</v>
+        <v>-0.9191985634332612</v>
       </c>
       <c r="L38" t="n">
-        <v>40.2338407392</v>
+        <v>40.41136047383443</v>
       </c>
       <c r="M38" t="n">
-        <v>0.169292235186</v>
+        <v>0.1578921668847098</v>
       </c>
       <c r="N38" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.396571931298</v>
+        <v>0.3965952392188052</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.278874862686</v>
+        <v>-0.2788660020949054</v>
       </c>
     </row>
     <row r="39">
@@ -2552,46 +2552,46 @@
         <v>7</v>
       </c>
       <c r="D39" t="n">
-        <v>0.39168284528</v>
+        <v>0.3916828452804821</v>
       </c>
       <c r="E39" t="n">
-        <v>0.39168284528</v>
+        <v>0.3916828452804842</v>
       </c>
       <c r="F39" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181794</v>
       </c>
       <c r="G39" t="n">
-        <v>24.1839446833</v>
+        <v>24.23570115180031</v>
       </c>
       <c r="H39" t="n">
-        <v>7.47261986983</v>
+        <v>7.479078755773887</v>
       </c>
       <c r="I39" t="n">
-        <v>3.36985168054</v>
+        <v>3.372939882578875</v>
       </c>
       <c r="J39" t="n">
-        <v>0.620390385421</v>
+        <v>0.5883677641103552</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.892435878132</v>
+        <v>-0.9191813121957401</v>
       </c>
       <c r="L39" t="n">
-        <v>41.4309198704</v>
+        <v>41.58383800434633</v>
       </c>
       <c r="M39" t="n">
-        <v>0.172565022687</v>
+        <v>0.1598798370207083</v>
       </c>
       <c r="N39" t="n">
-        <v>1.7763568394e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.396689579083</v>
+        <v>0.3967129489273589</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0.252612882233</v>
+        <v>-0.252578782880966</v>
       </c>
     </row>
     <row r="40">
@@ -2607,46 +2607,46 @@
         <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>0.380776153923</v>
+        <v>0.380776153923287</v>
       </c>
       <c r="E40" t="n">
-        <v>0.380776153923</v>
+        <v>0.3807761539232899</v>
       </c>
       <c r="F40" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181799</v>
       </c>
       <c r="G40" t="n">
-        <v>24.1939946436</v>
+        <v>24.23804690453995</v>
       </c>
       <c r="H40" t="n">
-        <v>7.45839578707</v>
+        <v>7.464771293785062</v>
       </c>
       <c r="I40" t="n">
-        <v>3.35624142308</v>
+        <v>3.359329516064235</v>
       </c>
       <c r="J40" t="n">
-        <v>0.666515706965</v>
+        <v>0.634467001319287</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.892323704288</v>
+        <v>-0.9190684714926153</v>
       </c>
       <c r="L40" t="n">
-        <v>40.5646484432</v>
+        <v>40.77200714763487</v>
       </c>
       <c r="M40" t="n">
-        <v>0.168777988416</v>
+        <v>0.1600815238716506</v>
       </c>
       <c r="N40" t="n">
-        <v>1.7763568394e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.396642430999</v>
+        <v>0.3966658485885495</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.266836964995</v>
+        <v>-0.2668862448697915</v>
       </c>
     </row>
     <row r="41">
@@ -2662,46 +2662,46 @@
         <v>9</v>
       </c>
       <c r="D41" t="n">
-        <v>0.382215671745</v>
+        <v>0.3822156717453015</v>
       </c>
       <c r="E41" t="n">
-        <v>0.382215671745</v>
+        <v>0.3822156717453033</v>
       </c>
       <c r="F41" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181793</v>
       </c>
       <c r="G41" t="n">
-        <v>24.2828930837</v>
+        <v>24.30895461415875</v>
       </c>
       <c r="H41" t="n">
-        <v>7.46087962683</v>
+        <v>7.467314843278041</v>
       </c>
       <c r="I41" t="n">
-        <v>3.35681618558</v>
+        <v>3.359906675407786</v>
       </c>
       <c r="J41" t="n">
-        <v>0.659737750286</v>
+        <v>0.6276877962362929</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.892499228134</v>
+        <v>-0.9192465901682133</v>
       </c>
       <c r="L41" t="n">
-        <v>40.5758237675</v>
+        <v>40.78518388305486</v>
       </c>
       <c r="M41" t="n">
-        <v>0.168591498835</v>
+        <v>0.1611281384621159</v>
       </c>
       <c r="N41" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.396611359576</v>
+        <v>0.396634722949432</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.264353125236</v>
+        <v>-0.2643426953768122</v>
       </c>
     </row>
     <row r="42">
@@ -2717,46 +2717,46 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.421900766336</v>
+        <v>0.4219007663355715</v>
       </c>
       <c r="E42" t="n">
-        <v>0.421900766336</v>
+        <v>0.4219007663355716</v>
       </c>
       <c r="F42" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181783</v>
       </c>
       <c r="G42" t="n">
-        <v>24.1717302639</v>
+        <v>24.23130582179189</v>
       </c>
       <c r="H42" t="n">
-        <v>7.50745711383</v>
+        <v>7.513899014922092</v>
       </c>
       <c r="I42" t="n">
-        <v>3.39644827262</v>
+        <v>3.399545385803161</v>
       </c>
       <c r="J42" t="n">
-        <v>0.494121153403</v>
+        <v>0.4621632334192809</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.892135680779</v>
+        <v>-0.9188832601043138</v>
       </c>
       <c r="L42" t="n">
-        <v>44.3908663188</v>
+        <v>44.53226464473642</v>
       </c>
       <c r="M42" t="n">
-        <v>0.16768699245</v>
+        <v>0.1586386704550016</v>
       </c>
       <c r="N42" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.396989807631</v>
+        <v>0.3970131772473535</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.217775638243</v>
+        <v>-0.2177585237327611</v>
       </c>
     </row>
     <row r="43">
@@ -2772,46 +2772,46 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.439650326898</v>
+        <v>0.4396503268984713</v>
       </c>
       <c r="E43" t="n">
-        <v>0.439650326898</v>
+        <v>0.4396503268984718</v>
       </c>
       <c r="F43" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181785</v>
       </c>
       <c r="G43" t="n">
-        <v>24.3414442088</v>
+        <v>24.39331555918055</v>
       </c>
       <c r="H43" t="n">
-        <v>7.52294786788</v>
+        <v>7.529454219317812</v>
       </c>
       <c r="I43" t="n">
-        <v>3.40946142621</v>
+        <v>3.412559360762868</v>
       </c>
       <c r="J43" t="n">
-        <v>0.420204510719</v>
+        <v>0.3882992626583561</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.891964481724</v>
+        <v>-0.9187108150111929</v>
       </c>
       <c r="L43" t="n">
-        <v>46.1512730054</v>
+        <v>46.23676538251535</v>
       </c>
       <c r="M43" t="n">
-        <v>0.166333315605</v>
+        <v>0.1562112131475977</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6645352591e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.397081896124</v>
+        <v>0.3971051866512374</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.202284884186</v>
+        <v>-0.2022033193370412</v>
       </c>
     </row>
     <row r="44">
@@ -2827,46 +2827,46 @@
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>0.421554727482</v>
+        <v>0.4215547274815467</v>
       </c>
       <c r="E44" t="n">
-        <v>0.421554727482</v>
+        <v>0.4215547274815461</v>
       </c>
       <c r="F44" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181778</v>
       </c>
       <c r="G44" t="n">
-        <v>24.2460673722</v>
+        <v>24.27201402076171</v>
       </c>
       <c r="H44" t="n">
-        <v>7.50409335499</v>
+        <v>7.510541821256909</v>
       </c>
       <c r="I44" t="n">
-        <v>3.39646192869</v>
+        <v>3.399562748329541</v>
       </c>
       <c r="J44" t="n">
-        <v>0.495514059362</v>
+        <v>0.4635556232667199</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.892075500062</v>
+        <v>-0.9188217653672608</v>
       </c>
       <c r="L44" t="n">
-        <v>44.3947513877</v>
+        <v>44.39687964641278</v>
       </c>
       <c r="M44" t="n">
-        <v>0.167795681671</v>
+        <v>0.1604247685247091</v>
       </c>
       <c r="N44" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.39695346277</v>
+        <v>0.3969768030112208</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.22113939708</v>
+        <v>-0.2211157173979448</v>
       </c>
     </row>
     <row r="45">
@@ -2882,46 +2882,46 @@
         <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>0.420140963516</v>
+        <v>0.420140963516072</v>
       </c>
       <c r="E45" t="n">
-        <v>0.420140963516</v>
+        <v>0.4201409635160733</v>
       </c>
       <c r="F45" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181789</v>
       </c>
       <c r="G45" t="n">
-        <v>24.1368989302</v>
+        <v>24.16284557876059</v>
       </c>
       <c r="H45" t="n">
-        <v>7.50771356089</v>
+        <v>7.514122870749873</v>
       </c>
       <c r="I45" t="n">
-        <v>3.39331564044</v>
+        <v>3.396413234523383</v>
       </c>
       <c r="J45" t="n">
-        <v>0.50173593627</v>
+        <v>0.4697780950797689</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.892084863287</v>
+        <v>-0.9188321041376293</v>
       </c>
       <c r="L45" t="n">
-        <v>44.4351705765</v>
+        <v>44.54390516634561</v>
       </c>
       <c r="M45" t="n">
-        <v>0.171801732679</v>
+        <v>0.1577514852685498</v>
       </c>
       <c r="N45" t="n">
-        <v>1.7763568394e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.396964059605</v>
+        <v>0.3969873811764075</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.217519191175</v>
+        <v>-0.2175346679049808</v>
       </c>
     </row>
     <row r="46">
@@ -2937,46 +2937,46 @@
         <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>0.439536255982</v>
+        <v>0.4395362559823265</v>
       </c>
       <c r="E46" t="n">
-        <v>0.439536255982</v>
+        <v>0.4395362559823259</v>
       </c>
       <c r="F46" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181777</v>
       </c>
       <c r="G46" t="n">
-        <v>24.2673929489</v>
+        <v>24.31144520988737</v>
       </c>
       <c r="H46" t="n">
-        <v>7.52257377841</v>
+        <v>7.52898728527263</v>
       </c>
       <c r="I46" t="n">
-        <v>3.39783689758</v>
+        <v>3.400945266958758</v>
       </c>
       <c r="J46" t="n">
-        <v>0.420403223398</v>
+        <v>0.3884910867749803</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.892084119548</v>
+        <v>-0.9188314106523929</v>
       </c>
       <c r="L46" t="n">
-        <v>46.2505066854</v>
+        <v>46.33392465593153</v>
       </c>
       <c r="M46" t="n">
-        <v>0.170617187132</v>
+        <v>0.155121790236504</v>
       </c>
       <c r="N46" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.397106172378</v>
+        <v>0.3971294709761646</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.202658973656</v>
+        <v>-0.2026702533822231</v>
       </c>
     </row>
     <row r="47">
@@ -2992,46 +2992,46 @@
         <v>5</v>
       </c>
       <c r="D47" t="n">
-        <v>0.434303723402</v>
+        <v>0.4343037234016767</v>
       </c>
       <c r="E47" t="n">
-        <v>0.434303723402</v>
+        <v>0.434303723401678</v>
       </c>
       <c r="F47" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181792</v>
       </c>
       <c r="G47" t="n">
-        <v>24.2651018475</v>
+        <v>24.29104849603343</v>
       </c>
       <c r="H47" t="n">
-        <v>7.52540772811</v>
+        <v>7.5317957558289</v>
       </c>
       <c r="I47" t="n">
-        <v>3.39635558105</v>
+        <v>3.3994678108906</v>
       </c>
       <c r="J47" t="n">
-        <v>0.44235565879</v>
+        <v>0.4104200299626137</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.8920167492660001</v>
+        <v>-0.9187666140083109</v>
       </c>
       <c r="L47" t="n">
-        <v>45.7797198634</v>
+        <v>45.93136143848666</v>
       </c>
       <c r="M47" t="n">
-        <v>0.171490418979</v>
+        <v>0.1587476198613569</v>
       </c>
       <c r="N47" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.39706420149</v>
+        <v>0.3970875433768495</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.199825023957</v>
+        <v>-0.1998617828259537</v>
       </c>
     </row>
     <row r="48">
@@ -3047,46 +3047,46 @@
         <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>0.421563700923</v>
+        <v>0.4215637009231368</v>
       </c>
       <c r="E48" t="n">
-        <v>0.421563700923</v>
+        <v>0.4215637009231368</v>
       </c>
       <c r="F48" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181781</v>
       </c>
       <c r="G48" t="n">
-        <v>24.2286881061</v>
+        <v>24.28044457457132</v>
       </c>
       <c r="H48" t="n">
-        <v>7.49160750278</v>
+        <v>7.498048368441363</v>
       </c>
       <c r="I48" t="n">
-        <v>3.37868917702</v>
+        <v>3.381775005277734</v>
       </c>
       <c r="J48" t="n">
-        <v>0.495502536067</v>
+        <v>0.4635411608030233</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.89213081505</v>
+        <v>-0.9188802046207231</v>
       </c>
       <c r="L48" t="n">
-        <v>44.0209047707</v>
+        <v>44.19842450531408</v>
       </c>
       <c r="M48" t="n">
-        <v>0.168597459966</v>
+        <v>0.1534529050040553</v>
       </c>
       <c r="N48" t="n">
-        <v>1.7763568394e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.396932717214</v>
+        <v>0.3969560032083677</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.233625249289</v>
+        <v>-0.2336091702134908</v>
       </c>
     </row>
     <row r="49">
@@ -3102,46 +3102,46 @@
         <v>7</v>
       </c>
       <c r="D49" t="n">
-        <v>0.435480119607</v>
+        <v>0.435480119607355</v>
       </c>
       <c r="E49" t="n">
-        <v>0.435480119607</v>
+        <v>0.4354801196073564</v>
       </c>
       <c r="F49" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181791</v>
       </c>
       <c r="G49" t="n">
-        <v>24.2040964919</v>
+        <v>24.25585296035181</v>
       </c>
       <c r="H49" t="n">
-        <v>7.52678250295</v>
+        <v>7.533231038636648</v>
       </c>
       <c r="I49" t="n">
-        <v>3.40911455709</v>
+        <v>3.412210766581422</v>
       </c>
       <c r="J49" t="n">
-        <v>0.437201065576</v>
+        <v>0.4052693082430541</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.892081206521</v>
+        <v>-0.9188295600465962</v>
       </c>
       <c r="L49" t="n">
-        <v>45.7695239115</v>
+        <v>45.9106491511376</v>
       </c>
       <c r="M49" t="n">
-        <v>0.169812643991</v>
+        <v>0.1558508483709008</v>
       </c>
       <c r="N49" t="n">
-        <v>1.7763568394e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.39708805928</v>
+        <v>0.3971113813831746</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.19845024912</v>
+        <v>-0.1984265000182051</v>
       </c>
     </row>
     <row r="50">
@@ -3157,46 +3157,46 @@
         <v>8</v>
       </c>
       <c r="D50" t="n">
-        <v>0.427494361645</v>
+        <v>0.4274943616454829</v>
       </c>
       <c r="E50" t="n">
-        <v>0.427494361645</v>
+        <v>0.4274943616454851</v>
       </c>
       <c r="F50" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181798</v>
       </c>
       <c r="G50" t="n">
-        <v>24.2126255936</v>
+        <v>24.24273494219831</v>
       </c>
       <c r="H50" t="n">
-        <v>7.51430205337</v>
+        <v>7.520659608222538</v>
       </c>
       <c r="I50" t="n">
-        <v>3.39815494766</v>
+        <v>3.401258518172799</v>
       </c>
       <c r="J50" t="n">
-        <v>0.471222747592</v>
+        <v>0.4392731441309526</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.891978588881</v>
+        <v>-0.9187262035476034</v>
       </c>
       <c r="L50" t="n">
-        <v>45.0670173778</v>
+        <v>45.28594979606218</v>
       </c>
       <c r="M50" t="n">
-        <v>0.165191109418</v>
+        <v>0.154559932519741</v>
       </c>
       <c r="N50" t="n">
-        <v>2.6645352591e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.39704264675</v>
+        <v>0.3970660544155449</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.210930698703</v>
+        <v>-0.2109979304323151</v>
       </c>
     </row>
     <row r="51">
@@ -3212,46 +3212,46 @@
         <v>9</v>
       </c>
       <c r="D51" t="n">
-        <v>0.422468875355</v>
+        <v>0.4224688753554956</v>
       </c>
       <c r="E51" t="n">
-        <v>0.422468875355</v>
+        <v>0.4224688753554974</v>
       </c>
       <c r="F51" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181794</v>
       </c>
       <c r="G51" t="n">
-        <v>24.2953280111</v>
+        <v>24.30744662919549</v>
       </c>
       <c r="H51" t="n">
-        <v>7.50993689316</v>
+        <v>7.516349595747092</v>
       </c>
       <c r="I51" t="n">
-        <v>3.39365867386</v>
+        <v>3.396757447347375</v>
       </c>
       <c r="J51" t="n">
-        <v>0.491562181354</v>
+        <v>0.4595945306135676</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.892135146028</v>
+        <v>-0.9188845478111838</v>
       </c>
       <c r="L51" t="n">
-        <v>44.4177826285</v>
+        <v>44.5312560394235</v>
       </c>
       <c r="M51" t="n">
-        <v>0.165085261846</v>
+        <v>0.1559410084934254</v>
       </c>
       <c r="N51" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0.396980394853</v>
+        <v>0.3970037180897368</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.215295858905</v>
+        <v>-0.2153079429077609</v>
       </c>
     </row>
     <row r="52">
@@ -3267,46 +3267,46 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0.443404919199</v>
+        <v>0.4434049191992604</v>
       </c>
       <c r="E52" t="n">
-        <v>0.443404919199</v>
+        <v>0.4434049191992602</v>
       </c>
       <c r="F52" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181781</v>
       </c>
       <c r="G52" t="n">
-        <v>24.1984106409</v>
+        <v>24.25798619878465</v>
       </c>
       <c r="H52" t="n">
-        <v>7.53635482671</v>
+        <v>7.542788593598989</v>
       </c>
       <c r="I52" t="n">
-        <v>3.41827164594</v>
+        <v>3.421376564046943</v>
       </c>
       <c r="J52" t="n">
-        <v>0.404051946453</v>
+        <v>0.3721362042310046</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.891981905843</v>
+        <v>-0.9187307849427737</v>
       </c>
       <c r="L52" t="n">
-        <v>46.4381919542</v>
+        <v>46.57959028012112</v>
       </c>
       <c r="M52" t="n">
-        <v>0.169013377864</v>
+        <v>0.1581990773410437</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6645352591e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0.397201208431</v>
+        <v>0.3972245707366648</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.188877925361</v>
+        <v>-0.188868945055864</v>
       </c>
     </row>
     <row r="53">
@@ -3322,46 +3322,46 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0.464897994365</v>
+        <v>0.4648979943653244</v>
       </c>
       <c r="E53" t="n">
-        <v>0.464897994365</v>
+        <v>0.4648979943653257</v>
       </c>
       <c r="F53" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518179</v>
       </c>
       <c r="G53" t="n">
-        <v>24.3173573913</v>
+        <v>24.36922874164907</v>
       </c>
       <c r="H53" t="n">
-        <v>7.55699937567</v>
+        <v>7.563459836739695</v>
       </c>
       <c r="I53" t="n">
-        <v>3.43328109079</v>
+        <v>3.436388473517461</v>
       </c>
       <c r="J53" t="n">
-        <v>0.314623765043</v>
+        <v>0.2827735546232212</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.891782934014</v>
+        <v>-0.9185306301371601</v>
       </c>
       <c r="L53" t="n">
-        <v>48.6550923296</v>
+        <v>48.74058470666804</v>
       </c>
       <c r="M53" t="n">
-        <v>0.164887061876</v>
+        <v>0.1513902681506528</v>
       </c>
       <c r="N53" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.397321717582</v>
+        <v>0.39734498565548</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.168233376401</v>
+        <v>-0.1681977019151581</v>
       </c>
     </row>
     <row r="54">
@@ -3377,46 +3377,46 @@
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>0.443816348976</v>
+        <v>0.4438163489764516</v>
       </c>
       <c r="E54" t="n">
-        <v>0.443816348976</v>
+        <v>0.4438163489764518</v>
       </c>
       <c r="F54" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181783</v>
       </c>
       <c r="G54" t="n">
-        <v>24.2470836614</v>
+        <v>24.2730303099959</v>
       </c>
       <c r="H54" t="n">
-        <v>7.53144561934</v>
+        <v>7.537882151390567</v>
       </c>
       <c r="I54" t="n">
-        <v>3.41243151862</v>
+        <v>3.415544265566645</v>
       </c>
       <c r="J54" t="n">
-        <v>0.40239562283</v>
+        <v>0.3704837339865664</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.891910466659</v>
+        <v>-0.9186577679679877</v>
       </c>
       <c r="L54" t="n">
-        <v>46.5663513003</v>
+        <v>46.56847955902534</v>
       </c>
       <c r="M54" t="n">
-        <v>0.167357273304</v>
+        <v>0.1592055074274194</v>
       </c>
       <c r="N54" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.397145340652</v>
+        <v>0.3971686687636775</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.193787132727</v>
+        <v>-0.193775387264286</v>
       </c>
     </row>
     <row r="55">
@@ -3432,46 +3432,46 @@
         <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>0.44561440677</v>
+        <v>0.4456144067700137</v>
       </c>
       <c r="E55" t="n">
-        <v>0.44561440677</v>
+        <v>0.4456144067700137</v>
       </c>
       <c r="F55" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181782</v>
       </c>
       <c r="G55" t="n">
-        <v>24.1452312014</v>
+        <v>24.17117784996387</v>
       </c>
       <c r="H55" t="n">
-        <v>7.54413704282</v>
+        <v>7.55052425355326</v>
       </c>
       <c r="I55" t="n">
-        <v>3.41470373153</v>
+        <v>3.417810608482978</v>
       </c>
       <c r="J55" t="n">
-        <v>0.395167955896</v>
+        <v>0.3632638951369921</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.891886245018</v>
+        <v>-0.9186348517414109</v>
       </c>
       <c r="L55" t="n">
-        <v>46.9474525224</v>
+        <v>47.05618711220559</v>
       </c>
       <c r="M55" t="n">
-        <v>0.171054787946</v>
+        <v>0.1559544218768092</v>
       </c>
       <c r="N55" t="n">
-        <v>4.4408920985e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.397211270257</v>
+        <v>0.3972345409857418</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.181095709246</v>
+        <v>-0.181133285101593</v>
       </c>
     </row>
     <row r="56">
@@ -3487,46 +3487,46 @@
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>0.464959926643</v>
+        <v>0.4649599266432179</v>
       </c>
       <c r="E56" t="n">
-        <v>0.464959926643</v>
+        <v>0.4649599266432183</v>
       </c>
       <c r="F56" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181782</v>
       </c>
       <c r="G56" t="n">
-        <v>24.3271991303</v>
+        <v>24.37125139132243</v>
       </c>
       <c r="H56" t="n">
-        <v>7.55223072197</v>
+        <v>7.55866767386695</v>
       </c>
       <c r="I56" t="n">
-        <v>3.42025244923</v>
+        <v>3.423367243007359</v>
       </c>
       <c r="J56" t="n">
-        <v>0.314063590456</v>
+        <v>0.2822081723257494</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.891916012871</v>
+        <v>-0.9186649948433662</v>
       </c>
       <c r="L56" t="n">
-        <v>48.6930771278</v>
+        <v>48.77649509837131</v>
       </c>
       <c r="M56" t="n">
-        <v>0.169293378517</v>
+        <v>0.1521016580461993</v>
       </c>
       <c r="N56" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.397323692195</v>
+        <v>0.3973469685901256</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.173002030098</v>
+        <v>-0.1729898647879029</v>
       </c>
     </row>
     <row r="57">
@@ -3542,46 +3542,46 @@
         <v>5</v>
       </c>
       <c r="D57" t="n">
-        <v>0.45988795581</v>
+        <v>0.4598879558096258</v>
       </c>
       <c r="E57" t="n">
-        <v>0.45988795581</v>
+        <v>0.4598879558096272</v>
       </c>
       <c r="F57" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518179</v>
       </c>
       <c r="G57" t="n">
-        <v>24.2785435106</v>
+        <v>24.30449015917259</v>
       </c>
       <c r="H57" t="n">
-        <v>7.55952086011</v>
+        <v>7.565904457390254</v>
       </c>
       <c r="I57" t="n">
-        <v>3.42062521578</v>
+        <v>3.42375170180419</v>
       </c>
       <c r="J57" t="n">
-        <v>0.335592208691</v>
+        <v>0.3037131899995975</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.891727609781</v>
+        <v>-0.9184781750713871</v>
       </c>
       <c r="L57" t="n">
-        <v>48.3549072683</v>
+        <v>48.48211573722887</v>
       </c>
       <c r="M57" t="n">
-        <v>0.165491355862</v>
+        <v>0.1537176868004206</v>
       </c>
       <c r="N57" t="n">
-        <v>3.5527136788e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0.397306620516</v>
+        <v>0.3973299290272816</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.165711891961</v>
+        <v>-0.1657530812645991</v>
       </c>
     </row>
     <row r="58">
@@ -3597,46 +3597,46 @@
         <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>0.445859138756</v>
+        <v>0.4458591387556534</v>
       </c>
       <c r="E58" t="n">
-        <v>0.445859138756</v>
+        <v>0.4458591387556536</v>
       </c>
       <c r="F58" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181781</v>
       </c>
       <c r="G58" t="n">
-        <v>24.2783651064</v>
+        <v>24.33012157482182</v>
       </c>
       <c r="H58" t="n">
-        <v>7.52440773561</v>
+        <v>7.530835854216178</v>
       </c>
       <c r="I58" t="n">
-        <v>3.40663719991</v>
+        <v>3.409730481399763</v>
       </c>
       <c r="J58" t="n">
-        <v>0.393949361447</v>
+        <v>0.3620391944689322</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.891947777014</v>
+        <v>-0.9186989821878232</v>
       </c>
       <c r="L58" t="n">
-        <v>46.5158258494</v>
+        <v>46.69334558404427</v>
       </c>
       <c r="M58" t="n">
-        <v>0.16603537796</v>
+        <v>0.1511231527700383</v>
       </c>
       <c r="N58" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.397175543704</v>
+        <v>0.3971988009626037</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.200825016457</v>
+        <v>-0.2008216844386759</v>
       </c>
     </row>
     <row r="59">
@@ -3652,46 +3652,46 @@
         <v>7</v>
       </c>
       <c r="D59" t="n">
-        <v>0.459291056117</v>
+        <v>0.459291056117239</v>
       </c>
       <c r="E59" t="n">
-        <v>0.459291056117</v>
+        <v>0.45929105611724</v>
       </c>
       <c r="F59" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G59" t="n">
-        <v>24.2083020705</v>
+        <v>24.26005853895265</v>
       </c>
       <c r="H59" t="n">
-        <v>7.56005128023</v>
+        <v>7.566491922462216</v>
       </c>
       <c r="I59" t="n">
-        <v>3.433265866</v>
+        <v>3.436368437174047</v>
       </c>
       <c r="J59" t="n">
-        <v>0.33776879778</v>
+        <v>0.305889681034305</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.891861942274</v>
+        <v>-0.9186116773776533</v>
       </c>
       <c r="L59" t="n">
-        <v>48.1397713442</v>
+        <v>48.28089658389239</v>
       </c>
       <c r="M59" t="n">
-        <v>0.16737354913</v>
+        <v>0.1527736167644122</v>
       </c>
       <c r="N59" t="n">
-        <v>6.66133814775e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0.397329753945</v>
+        <v>0.3973530455109835</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.165181471834</v>
+        <v>-0.1651656161926374</v>
       </c>
     </row>
     <row r="60">
@@ -3707,46 +3707,46 @@
         <v>8</v>
       </c>
       <c r="D60" t="n">
-        <v>0.453876851674</v>
+        <v>0.4538768516738628</v>
       </c>
       <c r="E60" t="n">
-        <v>0.453876851674</v>
+        <v>0.4538768516738652</v>
       </c>
       <c r="F60" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181799</v>
       </c>
       <c r="G60" t="n">
-        <v>24.2192357805</v>
+        <v>24.24934512913081</v>
       </c>
       <c r="H60" t="n">
-        <v>7.5499980736</v>
+        <v>7.556336580475139</v>
       </c>
       <c r="I60" t="n">
-        <v>3.42503222445</v>
+        <v>3.428139204544027</v>
       </c>
       <c r="J60" t="n">
-        <v>0.360976029618</v>
+        <v>0.3290880079580975</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.8917737454220001</v>
+        <v>-0.9185226905840247</v>
       </c>
       <c r="L60" t="n">
-        <v>47.6869465563</v>
+        <v>47.90587897456188</v>
       </c>
       <c r="M60" t="n">
-        <v>0.16333848287</v>
+        <v>0.1516392003985549</v>
       </c>
       <c r="N60" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0.397270189688</v>
+        <v>0.3972935595554017</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.175234678473</v>
+        <v>-0.1753209581797144</v>
       </c>
     </row>
     <row r="61">
@@ -3762,46 +3762,46 @@
         <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>0.447585860613</v>
+        <v>0.4475858606134302</v>
       </c>
       <c r="E61" t="n">
-        <v>0.447585860613</v>
+        <v>0.4475858606134318</v>
       </c>
       <c r="F61" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181794</v>
       </c>
       <c r="G61" t="n">
-        <v>24.297316177</v>
+        <v>24.30943479508229</v>
       </c>
       <c r="H61" t="n">
-        <v>7.54152597301</v>
+        <v>7.547923468459142</v>
       </c>
       <c r="I61" t="n">
-        <v>3.41825787143</v>
+        <v>3.421362172518196</v>
       </c>
       <c r="J61" t="n">
-        <v>0.386496752343</v>
+        <v>0.3545840801496677</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.891948799308</v>
+        <v>-0.9186993615798308</v>
       </c>
       <c r="L61" t="n">
-        <v>46.889709223</v>
+        <v>47.00318263395058</v>
       </c>
       <c r="M61" t="n">
-        <v>0.164310799652</v>
+        <v>0.1555094355389801</v>
       </c>
       <c r="N61" t="n">
-        <v>1.33226762955e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.39721336116</v>
+        <v>0.3972366487413979</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.183706779059</v>
+        <v>-0.1837340701957118</v>
       </c>
     </row>
     <row r="62">
@@ -3817,46 +3817,46 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0.471072637119</v>
+        <v>0.4710726371189683</v>
       </c>
       <c r="E62" t="n">
-        <v>0.471072637119</v>
+        <v>0.4710726371189681</v>
       </c>
       <c r="F62" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181779</v>
       </c>
       <c r="G62" t="n">
-        <v>24.2563835667</v>
+        <v>24.31595912451523</v>
       </c>
       <c r="H62" t="n">
-        <v>7.5696601512</v>
+        <v>7.57609682341536</v>
       </c>
       <c r="I62" t="n">
-        <v>3.44548574907</v>
+        <v>3.448597261259322</v>
       </c>
       <c r="J62" t="n">
-        <v>0.288451023082</v>
+        <v>0.2566022679774068</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.891787997857</v>
+        <v>-0.9185384564912744</v>
       </c>
       <c r="L62" t="n">
-        <v>49.1816319913</v>
+        <v>49.32303031731075</v>
       </c>
       <c r="M62" t="n">
-        <v>0.168039695094</v>
+        <v>0.1551763554154569</v>
       </c>
       <c r="N62" t="n">
-        <v>1.11022302463e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.397455363157</v>
+        <v>0.397478692276817</v>
       </c>
       <c r="Q62" t="n">
-        <v>-0.155572600866</v>
+        <v>-0.1555607152394938</v>
       </c>
     </row>
     <row r="63">
@@ -3872,46 +3872,46 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0.496295468377</v>
+        <v>0.4962954683765242</v>
       </c>
       <c r="E63" t="n">
-        <v>0.496295468377</v>
+        <v>0.4962954683765249</v>
       </c>
       <c r="F63" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G63" t="n">
-        <v>24.3827191861</v>
+        <v>24.43459053651375</v>
       </c>
       <c r="H63" t="n">
-        <v>7.60072566202</v>
+        <v>7.607186615479788</v>
       </c>
       <c r="I63" t="n">
-        <v>3.46999326802</v>
+        <v>3.473100007027756</v>
       </c>
       <c r="J63" t="n">
-        <v>0.18346700228</v>
+        <v>0.1516886995350822</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.891473481464</v>
+        <v>-0.9182220046803612</v>
       </c>
       <c r="L63" t="n">
-        <v>51.8383201784</v>
+        <v>51.92381255550349</v>
       </c>
       <c r="M63" t="n">
-        <v>0.160566292058</v>
+        <v>0.1469110401418552</v>
       </c>
       <c r="N63" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0.397632877713</v>
+        <v>0.3976560789427703</v>
       </c>
       <c r="Q63" t="n">
-        <v>-0.124507090053</v>
+        <v>-0.1244709231750649</v>
       </c>
     </row>
     <row r="64">
@@ -3927,46 +3927,46 @@
         <v>2</v>
       </c>
       <c r="D64" t="n">
-        <v>0.476176641286</v>
+        <v>0.4761766412857553</v>
       </c>
       <c r="E64" t="n">
-        <v>0.476176641286</v>
+        <v>0.4761766412857553</v>
       </c>
       <c r="F64" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181782</v>
       </c>
       <c r="G64" t="n">
-        <v>24.2977019355</v>
+        <v>24.32364858410504</v>
       </c>
       <c r="H64" t="n">
-        <v>7.56915358757</v>
+        <v>7.575603717037859</v>
       </c>
       <c r="I64" t="n">
-        <v>3.4415744504</v>
+        <v>3.444692949076354</v>
       </c>
       <c r="J64" t="n">
-        <v>0.267361681904</v>
+        <v>0.2355232190970128</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.891623139117</v>
+        <v>-0.9183717535801738</v>
       </c>
       <c r="L64" t="n">
-        <v>49.7610667284</v>
+        <v>49.76319498705455</v>
       </c>
       <c r="M64" t="n">
-        <v>0.163637340662</v>
+        <v>0.1540201174750606</v>
       </c>
       <c r="N64" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0.397442807205</v>
+        <v>0.3974660963398104</v>
       </c>
       <c r="Q64" t="n">
-        <v>-0.156079164503</v>
+        <v>-0.1560538216169949</v>
       </c>
     </row>
     <row r="65">
@@ -3982,46 +3982,46 @@
         <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>0.476081993149</v>
+        <v>0.4760819931489528</v>
       </c>
       <c r="E65" t="n">
-        <v>0.476081993149</v>
+        <v>0.4760819931489523</v>
       </c>
       <c r="F65" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181778</v>
       </c>
       <c r="G65" t="n">
-        <v>24.1575068918</v>
+        <v>24.18345354033142</v>
       </c>
       <c r="H65" t="n">
-        <v>7.58226274258</v>
+        <v>7.58862678991201</v>
       </c>
       <c r="I65" t="n">
-        <v>3.43881392091</v>
+        <v>3.441934648006357</v>
       </c>
       <c r="J65" t="n">
-        <v>0.267784187478</v>
+        <v>0.235947032909979</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.891661938031</v>
+        <v>-0.9184130181545921</v>
       </c>
       <c r="L65" t="n">
-        <v>50.0609965952</v>
+        <v>50.16973118497275</v>
       </c>
       <c r="M65" t="n">
-        <v>0.168952484043</v>
+        <v>0.1511203956745076</v>
       </c>
       <c r="N65" t="n">
-        <v>3.5527136788e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0.397478634688</v>
+        <v>0.3975018753214854</v>
       </c>
       <c r="Q65" t="n">
-        <v>-0.142970009488</v>
+        <v>-0.1430307487428433</v>
       </c>
     </row>
     <row r="66">
@@ -4037,46 +4037,46 @@
         <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>0.492957492703</v>
+        <v>0.4929574927033715</v>
       </c>
       <c r="E66" t="n">
-        <v>0.492957492703</v>
+        <v>0.4929574927033719</v>
       </c>
       <c r="F66" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181784</v>
       </c>
       <c r="G66" t="n">
-        <v>24.3485795968</v>
+        <v>24.39263185781839</v>
       </c>
       <c r="H66" t="n">
-        <v>7.58390020641</v>
+        <v>7.590341909604794</v>
       </c>
       <c r="I66" t="n">
-        <v>3.4399826454</v>
+        <v>3.443109456300875</v>
       </c>
       <c r="J66" t="n">
-        <v>0.197063151865</v>
+        <v>0.1652762302146715</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.891715954267</v>
+        <v>-0.9184673104111689</v>
       </c>
       <c r="L66" t="n">
-        <v>51.4022401277</v>
+        <v>51.48565809821427</v>
       </c>
       <c r="M66" t="n">
-        <v>0.168920046814</v>
+        <v>0.1504305241012113</v>
       </c>
       <c r="N66" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0.397577891067</v>
+        <v>0.3976011349548481</v>
       </c>
       <c r="Q66" t="n">
-        <v>-0.141332545663</v>
+        <v>-0.1413156290500597</v>
       </c>
     </row>
     <row r="67">
@@ -4092,46 +4092,46 @@
         <v>5</v>
       </c>
       <c r="D67" t="n">
-        <v>0.481620845771</v>
+        <v>0.4816208457706668</v>
       </c>
       <c r="E67" t="n">
-        <v>0.481620845771</v>
+        <v>0.4816208457706684</v>
       </c>
       <c r="F67" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181793</v>
       </c>
       <c r="G67" t="n">
-        <v>24.315916132</v>
+        <v>24.3202156607783</v>
       </c>
       <c r="H67" t="n">
-        <v>7.58933752582</v>
+        <v>7.595750020151366</v>
       </c>
       <c r="I67" t="n">
-        <v>3.44314841424</v>
+        <v>3.446284533847735</v>
       </c>
       <c r="J67" t="n">
-        <v>0.244906093994</v>
+        <v>0.2130790255426182</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.891507631388</v>
+        <v>-0.9182588477299487</v>
       </c>
       <c r="L67" t="n">
-        <v>50.5408631884</v>
+        <v>50.66807165735032</v>
       </c>
       <c r="M67" t="n">
-        <v>0.163808555051</v>
+        <v>0.1496484690992739</v>
       </c>
       <c r="N67" t="n">
-        <v>1.33226762955e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0.397532578783</v>
+        <v>0.3975558858402117</v>
       </c>
       <c r="Q67" t="n">
-        <v>-0.135895226248</v>
+        <v>-0.1359075185034877</v>
       </c>
     </row>
     <row r="68">
@@ -4147,46 +4147,46 @@
         <v>6</v>
       </c>
       <c r="D68" t="n">
-        <v>0.470777981683</v>
+        <v>0.4707779816828522</v>
       </c>
       <c r="E68" t="n">
-        <v>0.470777981683</v>
+        <v>0.4707779816828528</v>
       </c>
       <c r="F68" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181784</v>
       </c>
       <c r="G68" t="n">
-        <v>24.2852117229</v>
+        <v>24.33696819134751</v>
       </c>
       <c r="H68" t="n">
-        <v>7.55881605619</v>
+        <v>7.565227454501612</v>
       </c>
       <c r="I68" t="n">
-        <v>3.43297957451</v>
+        <v>3.436076976787873</v>
       </c>
       <c r="J68" t="n">
-        <v>0.289922556303</v>
+        <v>0.2580712629644473</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.891701972932</v>
+        <v>-0.9184539456732989</v>
       </c>
       <c r="L68" t="n">
-        <v>49.0413883705</v>
+        <v>49.19668915351514</v>
       </c>
       <c r="M68" t="n">
-        <v>0.165359457634</v>
+        <v>0.1487430065592156</v>
       </c>
       <c r="N68" t="n">
-        <v>3.5527136788e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0.397425850498</v>
+        <v>0.3974490702442339</v>
       </c>
       <c r="Q68" t="n">
-        <v>-0.166416695879</v>
+        <v>-0.1664300841532418</v>
       </c>
     </row>
     <row r="69">
@@ -4202,46 +4202,46 @@
         <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>0.484265459307</v>
+        <v>0.4842654593072763</v>
       </c>
       <c r="E69" t="n">
-        <v>0.484265459307</v>
+        <v>0.484265459307277</v>
       </c>
       <c r="F69" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181784</v>
       </c>
       <c r="G69" t="n">
-        <v>24.2991128204</v>
+        <v>24.35086928882932</v>
       </c>
       <c r="H69" t="n">
-        <v>7.58593714971</v>
+        <v>7.592391851662885</v>
       </c>
       <c r="I69" t="n">
-        <v>3.4520731759</v>
+        <v>3.455181558200313</v>
       </c>
       <c r="J69" t="n">
-        <v>0.233276704524</v>
+        <v>0.2014530644412823</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.891667776807</v>
+        <v>-0.9184199518631421</v>
       </c>
       <c r="L69" t="n">
-        <v>50.6284373455</v>
+        <v>50.80110796654077</v>
       </c>
       <c r="M69" t="n">
-        <v>0.167032221535</v>
+        <v>0.1505694619391643</v>
       </c>
       <c r="N69" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0.397547905942</v>
+        <v>0.397571160468462</v>
       </c>
       <c r="Q69" t="n">
-        <v>-0.139295602357</v>
+        <v>-0.1392656869919682</v>
       </c>
     </row>
     <row r="70">
@@ -4257,46 +4257,46 @@
         <v>8</v>
       </c>
       <c r="D70" t="n">
-        <v>0.479543031649</v>
+        <v>0.4795430316493021</v>
       </c>
       <c r="E70" t="n">
-        <v>0.479543031649</v>
+        <v>0.4795430316493041</v>
       </c>
       <c r="F70" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181799</v>
       </c>
       <c r="G70" t="n">
-        <v>24.249887419</v>
+        <v>24.27999676765044</v>
       </c>
       <c r="H70" t="n">
-        <v>7.57960193362</v>
+        <v>7.585945968313329</v>
       </c>
       <c r="I70" t="n">
-        <v>3.44912636719</v>
+        <v>3.452240246476867</v>
       </c>
       <c r="J70" t="n">
-        <v>0.253877316511</v>
+        <v>0.2220489253360975</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.8915441742370001</v>
+        <v>-0.9182940737097194</v>
       </c>
       <c r="L70" t="n">
-        <v>50.1964492774</v>
+        <v>50.41538169565063</v>
       </c>
       <c r="M70" t="n">
-        <v>0.16136969331</v>
+        <v>0.1471273150850138</v>
       </c>
       <c r="N70" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0.397509554505</v>
+        <v>0.3975328911508209</v>
       </c>
       <c r="Q70" t="n">
-        <v>-0.14563081845</v>
+        <v>-0.1457115703415246</v>
       </c>
     </row>
     <row r="71">
@@ -4312,46 +4312,46 @@
         <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>0.471594808958</v>
+        <v>0.4715948089579139</v>
       </c>
       <c r="E71" t="n">
-        <v>0.471594808958</v>
+        <v>0.4715948089579148</v>
       </c>
       <c r="F71" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181791</v>
       </c>
       <c r="G71" t="n">
-        <v>24.3599612952</v>
+        <v>24.37207991335421</v>
       </c>
       <c r="H71" t="n">
-        <v>7.56916206525</v>
+        <v>7.575576203600095</v>
       </c>
       <c r="I71" t="n">
-        <v>3.43523061953</v>
+        <v>3.438348501017585</v>
       </c>
       <c r="J71" t="n">
-        <v>0.286147050086</v>
+        <v>0.254290106827634</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.891756124833</v>
+        <v>-0.9185075684947842</v>
       </c>
       <c r="L71" t="n">
-        <v>49.3025493757</v>
+        <v>49.41602278656059</v>
       </c>
       <c r="M71" t="n">
-        <v>0.16010376856</v>
+        <v>0.1507452713928264</v>
       </c>
       <c r="N71" t="n">
-        <v>1.7763568394e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0.39742233505</v>
+        <v>0.3974455918683055</v>
       </c>
       <c r="Q71" t="n">
-        <v>-0.156070686822</v>
+        <v>-0.1560813350547585</v>
       </c>
     </row>
     <row r="72">
@@ -4367,46 +4367,46 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.50302657879</v>
+        <v>0.5030265787903658</v>
       </c>
       <c r="E72" t="n">
-        <v>0.50302657879</v>
+        <v>0.5030265787903668</v>
       </c>
       <c r="F72" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181789</v>
       </c>
       <c r="G72" t="n">
-        <v>24.2679101464</v>
+        <v>24.32748570420785</v>
       </c>
       <c r="H72" t="n">
-        <v>7.60340763311</v>
+        <v>7.609818179699335</v>
       </c>
       <c r="I72" t="n">
-        <v>3.46893879037</v>
+        <v>3.472058017954557</v>
       </c>
       <c r="J72" t="n">
-        <v>0.154933186181</v>
+        <v>0.1231673457039002</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.891558968112</v>
+        <v>-0.9183099526500555</v>
       </c>
       <c r="L72" t="n">
-        <v>52.3872844134</v>
+        <v>52.528682739398</v>
       </c>
       <c r="M72" t="n">
-        <v>0.167128438965</v>
+        <v>0.1522320677679778</v>
       </c>
       <c r="N72" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>0.397728845925</v>
+        <v>0.3977521241385502</v>
       </c>
       <c r="Q72" t="n">
-        <v>-0.121825118954</v>
+        <v>-0.1218393589555182</v>
       </c>
     </row>
     <row r="73">
@@ -4422,46 +4422,46 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>0.518640478123</v>
+        <v>0.5186404781226466</v>
       </c>
       <c r="E73" t="n">
-        <v>0.518640478123</v>
+        <v>0.5186404781226474</v>
       </c>
       <c r="F73" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G73" t="n">
-        <v>24.378692232</v>
+        <v>24.43056358233387</v>
       </c>
       <c r="H73" t="n">
-        <v>7.63143617463</v>
+        <v>7.637873741254929</v>
       </c>
       <c r="I73" t="n">
-        <v>3.49570794227</v>
+        <v>3.49881187184785</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0902733166154</v>
+        <v>0.05855041579061337</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.891258602513</v>
+        <v>-0.9180079042761479</v>
       </c>
       <c r="L73" t="n">
-        <v>54.047848019</v>
+        <v>54.13334039605983</v>
       </c>
       <c r="M73" t="n">
-        <v>0.157696914693</v>
+        <v>0.142585585250029</v>
       </c>
       <c r="N73" t="n">
-        <v>3.5527136788e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>0.397858471917</v>
+        <v>0.3978816229711502</v>
       </c>
       <c r="Q73" t="n">
-        <v>-0.0937965774368</v>
+        <v>-0.09378379739992404</v>
       </c>
     </row>
     <row r="74">
@@ -4477,46 +4477,46 @@
         <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>0.503163467577</v>
+        <v>0.503163467576505</v>
       </c>
       <c r="E74" t="n">
-        <v>0.503163467577</v>
+        <v>0.5031634675765058</v>
       </c>
       <c r="F74" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G74" t="n">
-        <v>24.3024731384</v>
+        <v>24.32841978694874</v>
       </c>
       <c r="H74" t="n">
-        <v>7.6049494808</v>
+        <v>7.61138103283164</v>
       </c>
       <c r="I74" t="n">
-        <v>3.4736522057</v>
+        <v>3.476767888577702</v>
       </c>
       <c r="J74" t="n">
-        <v>0.154607727377</v>
+        <v>0.122832303523938</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.891370687704</v>
+        <v>-0.9181201775134791</v>
       </c>
       <c r="L74" t="n">
-        <v>52.5400560569</v>
+        <v>52.54218431558908</v>
       </c>
       <c r="M74" t="n">
-        <v>0.161254562624</v>
+        <v>0.1506360208643895</v>
       </c>
       <c r="N74" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>0.397714604257</v>
+        <v>0.3977378375796179</v>
       </c>
       <c r="Q74" t="n">
-        <v>-0.120283271269</v>
+        <v>-0.1202765058232131</v>
       </c>
     </row>
     <row r="75">
@@ -4532,46 +4532,46 @@
         <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>0.504557682249</v>
+        <v>0.5045576822493966</v>
       </c>
       <c r="E75" t="n">
-        <v>0.504557682249</v>
+        <v>0.5045576822493967</v>
       </c>
       <c r="F75" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181781</v>
       </c>
       <c r="G75" t="n">
-        <v>24.1891298207</v>
+        <v>24.24088628911061</v>
       </c>
       <c r="H75" t="n">
-        <v>7.61773715994</v>
+        <v>7.624119805026765</v>
       </c>
       <c r="I75" t="n">
-        <v>3.46761086095</v>
+        <v>3.470734013403479</v>
       </c>
       <c r="J75" t="n">
-        <v>0.148899142196</v>
+        <v>0.1171292905682651</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.891435288344</v>
+        <v>-0.9181884257670853</v>
       </c>
       <c r="L75" t="n">
-        <v>52.867409694</v>
+        <v>52.9761442837527</v>
       </c>
       <c r="M75" t="n">
-        <v>0.162234819511</v>
+        <v>0.1426174193310785</v>
       </c>
       <c r="N75" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0.397750549523</v>
+        <v>0.3977737228137403</v>
       </c>
       <c r="Q75" t="n">
-        <v>-0.107495592124</v>
+        <v>-0.1075377336280887</v>
       </c>
     </row>
     <row r="76">
@@ -4587,46 +4587,46 @@
         <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>0.521299377608</v>
+        <v>0.5212993776077141</v>
       </c>
       <c r="E76" t="n">
-        <v>0.521299377608</v>
+        <v>0.5212993776077141</v>
       </c>
       <c r="F76" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181781</v>
       </c>
       <c r="G76" t="n">
-        <v>24.3627982528</v>
+        <v>24.406850513743</v>
       </c>
       <c r="H76" t="n">
-        <v>7.62249305178</v>
+        <v>7.628910902643105</v>
       </c>
       <c r="I76" t="n">
-        <v>3.47034921599</v>
+        <v>3.47347638044667</v>
       </c>
       <c r="J76" t="n">
-        <v>0.0785453673694</v>
+        <v>0.04682853392394207</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.891492048093</v>
+        <v>-0.9182446855237484</v>
       </c>
       <c r="L76" t="n">
-        <v>54.2673752085</v>
+        <v>54.35079317908797</v>
       </c>
       <c r="M76" t="n">
-        <v>0.166901772592</v>
+        <v>0.1456512240115138</v>
       </c>
       <c r="N76" t="n">
-        <v>2.6645352591e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>0.397849277196</v>
+        <v>0.3978724333922063</v>
       </c>
       <c r="Q76" t="n">
-        <v>-0.102739700287</v>
+        <v>-0.1027466360117479</v>
       </c>
     </row>
     <row r="77">
@@ -4642,46 +4642,46 @@
         <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>0.508988812172</v>
+        <v>0.5089888121715609</v>
       </c>
       <c r="E77" t="n">
-        <v>0.508988812172</v>
+        <v>0.5089888121715622</v>
       </c>
       <c r="F77" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518179</v>
       </c>
       <c r="G77" t="n">
-        <v>24.3224509369</v>
+        <v>24.32675046567948</v>
       </c>
       <c r="H77" t="n">
-        <v>7.62660375338</v>
+        <v>7.632992153415649</v>
       </c>
       <c r="I77" t="n">
-        <v>3.47322965727</v>
+        <v>3.476370950489059</v>
       </c>
       <c r="J77" t="n">
-        <v>0.130621216091</v>
+        <v>0.09886207134791662</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.891250762539</v>
+        <v>-0.9180027344334748</v>
       </c>
       <c r="L77" t="n">
-        <v>53.298945884</v>
+        <v>53.41341216660862</v>
       </c>
       <c r="M77" t="n">
-        <v>0.162760953304</v>
+        <v>0.1489759401413625</v>
       </c>
       <c r="N77" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>0.397803265995</v>
+        <v>0.3978265033864121</v>
       </c>
       <c r="Q77" t="n">
-        <v>-0.09862899869199999</v>
+        <v>-0.09866538523920454</v>
       </c>
     </row>
     <row r="78">
@@ -4697,46 +4697,46 @@
         <v>6</v>
       </c>
       <c r="D78" t="n">
-        <v>0.498796063028</v>
+        <v>0.4987960630284027</v>
       </c>
       <c r="E78" t="n">
-        <v>0.498796063028</v>
+        <v>0.498796063028403</v>
       </c>
       <c r="F78" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181782</v>
       </c>
       <c r="G78" t="n">
-        <v>24.3332277051</v>
+        <v>24.38498417351145</v>
       </c>
       <c r="H78" t="n">
-        <v>7.58998057079</v>
+        <v>7.596397259428641</v>
       </c>
       <c r="I78" t="n">
-        <v>3.45504620184</v>
+        <v>3.458156293007492</v>
       </c>
       <c r="J78" t="n">
-        <v>0.17275451633</v>
+        <v>0.1409742180096691</v>
       </c>
       <c r="K78" t="n">
-        <v>-0.891470493016</v>
+        <v>-0.9182223785228083</v>
       </c>
       <c r="L78" t="n">
-        <v>51.8078515717</v>
+        <v>51.96315235472021</v>
       </c>
       <c r="M78" t="n">
-        <v>0.166204981986</v>
+        <v>0.1495657261142468</v>
       </c>
       <c r="N78" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>0.397678339529</v>
+        <v>0.3977015227177165</v>
       </c>
       <c r="Q78" t="n">
-        <v>-0.135252181279</v>
+        <v>-0.1352602792262125</v>
       </c>
     </row>
     <row r="79">
@@ -4752,46 +4752,46 @@
         <v>7</v>
       </c>
       <c r="D79" t="n">
-        <v>0.515972582912</v>
+        <v>0.5159725829121468</v>
       </c>
       <c r="E79" t="n">
-        <v>0.515972582912</v>
+        <v>0.5159725829121473</v>
       </c>
       <c r="F79" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181784</v>
       </c>
       <c r="G79" t="n">
-        <v>24.3383082053</v>
+        <v>24.39006467380886</v>
       </c>
       <c r="H79" t="n">
-        <v>7.62827726249</v>
+        <v>7.634727120262985</v>
       </c>
       <c r="I79" t="n">
-        <v>3.48880198599</v>
+        <v>3.491917861942057</v>
       </c>
       <c r="J79" t="n">
-        <v>0.100994407299</v>
+        <v>0.0692524970016189</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.891380194421</v>
+        <v>-0.9181331653782842</v>
       </c>
       <c r="L79" t="n">
-        <v>53.836798938</v>
+        <v>54.00946955912536</v>
       </c>
       <c r="M79" t="n">
-        <v>0.16179333935</v>
+        <v>0.1457881159158587</v>
       </c>
       <c r="N79" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>0.397862135884</v>
+        <v>0.3978853321399061</v>
       </c>
       <c r="Q79" t="n">
-        <v>-0.096955489581</v>
+        <v>-0.09693041839186822</v>
       </c>
     </row>
     <row r="80">
@@ -4807,46 +4807,46 @@
         <v>8</v>
       </c>
       <c r="D80" t="n">
-        <v>0.508615143736</v>
+        <v>0.5086151437357815</v>
       </c>
       <c r="E80" t="n">
-        <v>0.508615143736</v>
+        <v>0.5086151437357843</v>
       </c>
       <c r="F80" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181805</v>
       </c>
       <c r="G80" t="n">
-        <v>24.2795552536</v>
+        <v>24.30966460226116</v>
       </c>
       <c r="H80" t="n">
-        <v>7.61609943849</v>
+        <v>7.62244104654935</v>
       </c>
       <c r="I80" t="n">
-        <v>3.47608832621</v>
+        <v>3.479207992531883</v>
       </c>
       <c r="J80" t="n">
-        <v>0.132315789141</v>
+        <v>0.1005541844617505</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.891295858467</v>
+        <v>-0.9180474767483169</v>
       </c>
       <c r="L80" t="n">
-        <v>53.0611852805</v>
+        <v>53.19602388839832</v>
       </c>
       <c r="M80" t="n">
-        <v>0.159015371222</v>
+        <v>0.1463270570842259</v>
       </c>
       <c r="N80" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0.397780761784</v>
+        <v>0.3978040449504041</v>
       </c>
       <c r="Q80" t="n">
-        <v>-0.109133313578</v>
+        <v>-0.109216492105503</v>
       </c>
     </row>
     <row r="81">
@@ -4862,46 +4862,46 @@
         <v>9</v>
       </c>
       <c r="D81" t="n">
-        <v>0.502137014791</v>
+        <v>0.5021370147909322</v>
       </c>
       <c r="E81" t="n">
-        <v>0.502137014791</v>
+        <v>0.5021370147909328</v>
       </c>
       <c r="F81" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G81" t="n">
-        <v>24.3919301969</v>
+        <v>24.42985863495587</v>
       </c>
       <c r="H81" t="n">
-        <v>7.60618869405</v>
+        <v>7.612627265225998</v>
       </c>
       <c r="I81" t="n">
-        <v>3.46717982992</v>
+        <v>3.470301882543221</v>
       </c>
       <c r="J81" t="n">
-        <v>0.158622578463</v>
+        <v>0.126836225056284</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.891541150818</v>
+        <v>-0.9182943593201065</v>
       </c>
       <c r="L81" t="n">
-        <v>52.2885448012</v>
+        <v>52.40201821210544</v>
       </c>
       <c r="M81" t="n">
-        <v>0.158111702813</v>
+        <v>0.1465380804978658</v>
       </c>
       <c r="N81" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.397716685844</v>
+        <v>0.3977398986971061</v>
       </c>
       <c r="Q81" t="n">
-        <v>-0.119044058022</v>
+        <v>-0.1190302734288551</v>
       </c>
     </row>
     <row r="82">
@@ -4917,46 +4917,46 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0.531674230935</v>
+        <v>0.5316742309351408</v>
       </c>
       <c r="E82" t="n">
-        <v>0.531674230935</v>
+        <v>0.5316742309351417</v>
       </c>
       <c r="F82" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518179</v>
       </c>
       <c r="G82" t="n">
-        <v>24.2784360819</v>
+        <v>24.33801163974843</v>
       </c>
       <c r="H82" t="n">
-        <v>7.64089622997</v>
+        <v>7.647292406263936</v>
       </c>
       <c r="I82" t="n">
-        <v>3.49933131285</v>
+        <v>3.502447008596819</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0351375523749</v>
+        <v>0.003438836256447193</v>
       </c>
       <c r="K82" t="n">
-        <v>-0.8913376898749999</v>
+        <v>-0.9180905268736658</v>
       </c>
       <c r="L82" t="n">
-        <v>55.2089188889</v>
+        <v>55.35031721491235</v>
       </c>
       <c r="M82" t="n">
-        <v>0.166275386991</v>
+        <v>0.1502679901754748</v>
       </c>
       <c r="N82" t="n">
-        <v>1.11022302463e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0.39799203194</v>
+        <v>0.3980152472428184</v>
       </c>
       <c r="Q82" t="n">
-        <v>-0.0843365220974</v>
+        <v>-0.08436513239091692</v>
       </c>
     </row>
     <row r="83">
@@ -4972,46 +4972,46 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>0.539001382663</v>
+        <v>0.5390013826629285</v>
       </c>
       <c r="E83" t="n">
-        <v>0.539001382663</v>
+        <v>0.5390013826629292</v>
       </c>
       <c r="F83" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181785</v>
       </c>
       <c r="G83" t="n">
-        <v>24.3911836507</v>
+        <v>24.4430550010776</v>
       </c>
       <c r="H83" t="n">
-        <v>7.65435519173</v>
+        <v>7.660787641689443</v>
       </c>
       <c r="I83" t="n">
-        <v>3.51479047011</v>
+        <v>3.517897735464817</v>
       </c>
       <c r="J83" t="n">
-        <v>0.00507163606704</v>
+        <v>-0.02660392214299237</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.891093363122</v>
+        <v>-0.9178440190710502</v>
       </c>
       <c r="L83" t="n">
-        <v>56.0095873443</v>
+        <v>56.09507972135478</v>
       </c>
       <c r="M83" t="n">
-        <v>0.155341092285</v>
+        <v>0.1385956935721473</v>
       </c>
       <c r="N83" t="n">
-        <v>1.7763568394e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>0.398046313826</v>
+        <v>0.3980694372912408</v>
       </c>
       <c r="Q83" t="n">
-        <v>-0.07087756033500001</v>
+        <v>-0.07086989696541046</v>
       </c>
     </row>
     <row r="84">
@@ -5027,46 +5027,46 @@
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>0.52922894197</v>
+        <v>0.5292289419701585</v>
       </c>
       <c r="E84" t="n">
-        <v>0.52922894197</v>
+        <v>0.5292289419701595</v>
       </c>
       <c r="F84" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181791</v>
       </c>
       <c r="G84" t="n">
-        <v>24.3361434877</v>
+        <v>24.36209013624106</v>
       </c>
       <c r="H84" t="n">
-        <v>7.63830668624</v>
+        <v>7.644731168855097</v>
       </c>
       <c r="I84" t="n">
-        <v>3.49843706672</v>
+        <v>3.501559980898075</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0456991260793</v>
+        <v>0.01398820155461037</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.891151908325</v>
+        <v>-0.9179019416532558</v>
       </c>
       <c r="L84" t="n">
-        <v>55.039490655</v>
+        <v>55.04161891363793</v>
       </c>
       <c r="M84" t="n">
-        <v>0.157685442808</v>
+        <v>0.1456702247601243</v>
       </c>
       <c r="N84" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>0.397954590248</v>
+        <v>0.3979777624894179</v>
       </c>
       <c r="Q84" t="n">
-        <v>-0.0869260658281</v>
+        <v>-0.08692636979975621</v>
       </c>
     </row>
     <row r="85">
@@ -5082,46 +5082,46 @@
         <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>0.529576802283</v>
+        <v>0.529576802282729</v>
       </c>
       <c r="E85" t="n">
-        <v>0.529576802283</v>
+        <v>0.5295768022827289</v>
       </c>
       <c r="F85" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181778</v>
       </c>
       <c r="G85" t="n">
-        <v>24.1893803653</v>
+        <v>24.24113683379748</v>
       </c>
       <c r="H85" t="n">
-        <v>7.65225727513</v>
+        <v>7.658617718022849</v>
       </c>
       <c r="I85" t="n">
-        <v>3.4945944254</v>
+        <v>3.497717604203682</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0444230252613</v>
+        <v>0.01271376505810646</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.8912076730539999</v>
+        <v>-0.9179617870758813</v>
       </c>
       <c r="L85" t="n">
-        <v>55.3547076158</v>
+        <v>55.46344220556249</v>
       </c>
       <c r="M85" t="n">
-        <v>0.15985348492</v>
+        <v>0.1396496812694028</v>
       </c>
       <c r="N85" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>0.397998080345</v>
+        <v>0.398021207839913</v>
       </c>
       <c r="Q85" t="n">
-        <v>-0.0729754769347</v>
+        <v>-0.07303982063200465</v>
       </c>
     </row>
     <row r="86">
@@ -5137,46 +5137,46 @@
         <v>4</v>
       </c>
       <c r="D86" t="n">
-        <v>0.543502803596</v>
+        <v>0.5435028035964204</v>
       </c>
       <c r="E86" t="n">
-        <v>0.543502803596</v>
+        <v>0.5435028035964207</v>
       </c>
       <c r="F86" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518178</v>
       </c>
       <c r="G86" t="n">
-        <v>24.3709200984</v>
+        <v>24.41497235939685</v>
       </c>
       <c r="H86" t="n">
-        <v>7.64497517843</v>
+        <v>7.651385758907397</v>
       </c>
       <c r="I86" t="n">
-        <v>3.49111434461</v>
+        <v>3.494242000688079</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.014239830657</v>
+        <v>-0.04589965930736596</v>
       </c>
       <c r="K86" t="n">
-        <v>-0.8913066412540001</v>
+        <v>-0.918059894413946</v>
       </c>
       <c r="L86" t="n">
-        <v>56.5317222674</v>
+        <v>56.61514023799923</v>
       </c>
       <c r="M86" t="n">
-        <v>0.16455805386</v>
+        <v>0.1432542054826826</v>
       </c>
       <c r="N86" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0.398048709776</v>
+        <v>0.3980718107244701</v>
       </c>
       <c r="Q86" t="n">
-        <v>-0.0802575736392</v>
+        <v>-0.08027177974745658</v>
       </c>
     </row>
     <row r="87">
@@ -5192,46 +5192,46 @@
         <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>0.53064543494</v>
+        <v>0.5306454349404721</v>
       </c>
       <c r="E87" t="n">
-        <v>0.53064543494</v>
+        <v>0.5306454349404738</v>
       </c>
       <c r="F87" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181793</v>
       </c>
       <c r="G87" t="n">
-        <v>24.3346529357</v>
+        <v>24.33895246443432</v>
       </c>
       <c r="H87" t="n">
-        <v>7.6502550453</v>
+        <v>7.656636026731081</v>
       </c>
       <c r="I87" t="n">
-        <v>3.48875871258</v>
+        <v>3.491907296110435</v>
       </c>
       <c r="J87" t="n">
-        <v>0.0401850770458</v>
+        <v>0.008479114613471549</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.891035661274</v>
+        <v>-0.917788357534139</v>
       </c>
       <c r="L87" t="n">
-        <v>55.3930834925</v>
+        <v>55.50754977519</v>
       </c>
       <c r="M87" t="n">
-        <v>0.160804127355</v>
+        <v>0.1473490401639737</v>
       </c>
       <c r="N87" t="n">
-        <v>2.6645352591e-15</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0.398020301311</v>
+        <v>0.3980435010156513</v>
       </c>
       <c r="Q87" t="n">
-        <v>-0.07497770676399999</v>
+        <v>-0.07502151192377227</v>
       </c>
     </row>
     <row r="88">
@@ -5247,46 +5247,46 @@
         <v>6</v>
       </c>
       <c r="D88" t="n">
-        <v>0.526810296369</v>
+        <v>0.5268102963687114</v>
       </c>
       <c r="E88" t="n">
-        <v>0.526810296369</v>
+        <v>0.5268102963687109</v>
       </c>
       <c r="F88" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181775</v>
       </c>
       <c r="G88" t="n">
-        <v>24.3650668137</v>
+        <v>24.40288036975342</v>
       </c>
       <c r="H88" t="n">
-        <v>7.62434497673</v>
+        <v>7.630750423575751</v>
       </c>
       <c r="I88" t="n">
-        <v>3.47695495058</v>
+        <v>3.480072142817786</v>
       </c>
       <c r="J88" t="n">
-        <v>0.0556337963175</v>
+        <v>0.02392098297767497</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.891287330565</v>
+        <v>-0.9180408888879499</v>
       </c>
       <c r="L88" t="n">
-        <v>54.6082649892</v>
+        <v>54.68894872715573</v>
       </c>
       <c r="M88" t="n">
-        <v>0.164281135724</v>
+        <v>0.1478355899284514</v>
       </c>
       <c r="N88" t="n">
-        <v>2.6645352591e-15</v>
+        <v>1.110223024625157e-15</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>0.397922932592</v>
+        <v>0.3979460683208251</v>
       </c>
       <c r="Q88" t="n">
-        <v>-0.100887775342</v>
+        <v>-0.1009071150791021</v>
       </c>
     </row>
     <row r="89">
@@ -5302,46 +5302,46 @@
         <v>7</v>
       </c>
       <c r="D89" t="n">
-        <v>0.536946893186</v>
+        <v>0.5369468931855575</v>
       </c>
       <c r="E89" t="n">
-        <v>0.536946893186</v>
+        <v>0.5369468931855581</v>
       </c>
       <c r="F89" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G89" t="n">
-        <v>24.3537158585</v>
+        <v>24.40547232693114</v>
       </c>
       <c r="H89" t="n">
-        <v>7.65427900734</v>
+        <v>7.660734840397931</v>
       </c>
       <c r="I89" t="n">
-        <v>3.50841134761</v>
+        <v>3.511532520102938</v>
       </c>
       <c r="J89" t="n">
-        <v>0.0134171697774</v>
+        <v>-0.01827229300638583</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.891183734104</v>
+        <v>-0.9179374952414021</v>
       </c>
       <c r="L89" t="n">
-        <v>55.8956495232</v>
+        <v>56.0683201443006</v>
       </c>
       <c r="M89" t="n">
-        <v>0.159292165487</v>
+        <v>0.1433966859633158</v>
       </c>
       <c r="N89" t="n">
-        <v>4.4408920985e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>0.398064396683</v>
+        <v>0.3980875552885725</v>
       </c>
       <c r="Q89" t="n">
-        <v>-0.070953744727</v>
+        <v>-0.07092269825692199</v>
       </c>
     </row>
     <row r="90">
@@ -5357,46 +5357,46 @@
         <v>8</v>
       </c>
       <c r="D90" t="n">
-        <v>0.5273042548270001</v>
+        <v>0.5273042548268834</v>
       </c>
       <c r="E90" t="n">
-        <v>0.5273042548270001</v>
+        <v>0.5273042548268857</v>
       </c>
       <c r="F90" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181805</v>
       </c>
       <c r="G90" t="n">
-        <v>24.2813622432</v>
+        <v>24.31147159181996</v>
       </c>
       <c r="H90" t="n">
-        <v>7.63689819927</v>
+        <v>7.643229874570203</v>
       </c>
       <c r="I90" t="n">
-        <v>3.49310235764</v>
+        <v>3.496220010889286</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0541305548638</v>
+        <v>0.02241244518036935</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.891152398964</v>
+        <v>-0.917904953950074</v>
       </c>
       <c r="L90" t="n">
-        <v>54.8714077052</v>
+        <v>55.00624631310234</v>
       </c>
       <c r="M90" t="n">
-        <v>0.158365664023</v>
+        <v>0.1459532688706494</v>
       </c>
       <c r="N90" t="n">
-        <v>3.5527136788e-15</v>
+        <v>1.332267629550188e-15</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0.397964839728</v>
+        <v>0.3979880916825258</v>
       </c>
       <c r="Q90" t="n">
-        <v>-0.08833455279870001</v>
+        <v>-0.08842766408465064</v>
       </c>
     </row>
     <row r="91">
@@ -5412,46 +5412,46 @@
         <v>9</v>
       </c>
       <c r="D91" t="n">
-        <v>0.523148491915</v>
+        <v>0.5231484919146778</v>
       </c>
       <c r="E91" t="n">
-        <v>0.523148491915</v>
+        <v>0.5231484919146785</v>
       </c>
       <c r="F91" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181787</v>
       </c>
       <c r="G91" t="n">
-        <v>24.4687923941</v>
+        <v>24.50672083207252</v>
       </c>
       <c r="H91" t="n">
-        <v>7.63246376334</v>
+        <v>7.638928485989323</v>
       </c>
       <c r="I91" t="n">
-        <v>3.48489191797</v>
+        <v>3.488022955682359</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0708746098136</v>
+        <v>0.03914098228713941</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.891331950413</v>
+        <v>-0.9180861074710461</v>
       </c>
       <c r="L91" t="n">
-        <v>54.4050757622</v>
+        <v>54.51854917309833</v>
       </c>
       <c r="M91" t="n">
-        <v>0.158309616659</v>
+        <v>0.1461504791782882</v>
       </c>
       <c r="N91" t="n">
-        <v>3.5527136788e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0.397916795562</v>
+        <v>0.3979399817428102</v>
       </c>
       <c r="Q91" t="n">
-        <v>-0.0927689887276</v>
+        <v>-0.09272905266553089</v>
       </c>
     </row>
     <row r="92">
@@ -5464,46 +5464,46 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.603373358826</v>
+        <v>0.6033733588255475</v>
       </c>
       <c r="E92" t="n">
-        <v>0.603373358826</v>
+        <v>0.603373358825548</v>
       </c>
       <c r="F92" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518179</v>
       </c>
       <c r="G92" t="n">
-        <v>24.358895981</v>
+        <v>24.40646780261884</v>
       </c>
       <c r="H92" t="n">
-        <v>7.73057161273</v>
+        <v>7.736945973778845</v>
       </c>
       <c r="I92" t="n">
-        <v>3.56934884019</v>
+        <v>3.572481495287235</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.264208005342</v>
+        <v>-0.2957160850851588</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.890728688644</v>
+        <v>-0.9174855624316763</v>
       </c>
       <c r="L92" t="n">
-        <v>62.354196749</v>
+        <v>62.55934391624157</v>
       </c>
       <c r="M92" t="n">
-        <v>0.156823982947</v>
+        <v>0.1419131475885343</v>
       </c>
       <c r="N92" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>0.398672319579</v>
+        <v>0.3986953890235909</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.00533886066514</v>
+        <v>0.005288435123991242</v>
       </c>
     </row>
     <row r="93">
@@ -5516,46 +5516,46 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0.613597100249</v>
+        <v>0.6135971002488616</v>
       </c>
       <c r="E93" t="n">
-        <v>0.613597100249</v>
+        <v>0.6135971002488628</v>
       </c>
       <c r="F93" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181793</v>
       </c>
       <c r="G93" t="n">
-        <v>24.4420444545</v>
+        <v>24.49391580485973</v>
       </c>
       <c r="H93" t="n">
-        <v>7.74739096966</v>
+        <v>7.753769974774494</v>
       </c>
       <c r="I93" t="n">
-        <v>3.58850824224</v>
+        <v>3.591622018717584</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.306512185706</v>
+        <v>-0.3379848616548088</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.890494541402</v>
+        <v>-0.9172489156421143</v>
       </c>
       <c r="L93" t="n">
-        <v>63.5491051931</v>
+        <v>63.67561971694867</v>
       </c>
       <c r="M93" t="n">
-        <v>0.149182877576</v>
+        <v>0.1312344325191285</v>
       </c>
       <c r="N93" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>0.398770184359</v>
+        <v>0.3987931064936918</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.0221582175871</v>
+        <v>0.02211243611964075</v>
       </c>
     </row>
     <row r="94">
@@ -5568,46 +5568,46 @@
         <v>2</v>
       </c>
       <c r="D94" t="n">
-        <v>0.599282386094</v>
+        <v>0.5992823860941676</v>
       </c>
       <c r="E94" t="n">
-        <v>0.599282386094</v>
+        <v>0.5992823860941677</v>
       </c>
       <c r="F94" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518178</v>
       </c>
       <c r="G94" t="n">
-        <v>24.4072110124</v>
+        <v>24.42545345348761</v>
       </c>
       <c r="H94" t="n">
-        <v>7.72805151925</v>
+        <v>7.734461952192205</v>
       </c>
       <c r="I94" t="n">
-        <v>3.56710673949</v>
+        <v>3.570231602043727</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.246860160162</v>
+        <v>-0.2783800877292945</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.890602377254</v>
+        <v>-0.9173561726012416</v>
       </c>
       <c r="L94" t="n">
-        <v>61.9768778098</v>
+        <v>62.00124341606957</v>
       </c>
       <c r="M94" t="n">
-        <v>0.151757459596</v>
+        <v>0.1398410317648744</v>
       </c>
       <c r="N94" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>0.398627239477</v>
+        <v>0.3986502495833351</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.00281876718214</v>
+        <v>0.00280441353735128</v>
       </c>
     </row>
     <row r="95">
@@ -5620,46 +5620,46 @@
         <v>3</v>
       </c>
       <c r="D95" t="n">
-        <v>0.599939617074</v>
+        <v>0.5999396170742373</v>
       </c>
       <c r="E95" t="n">
-        <v>0.599939617074</v>
+        <v>0.5999396170742367</v>
       </c>
       <c r="F95" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181775</v>
       </c>
       <c r="G95" t="n">
-        <v>24.2727740219</v>
+        <v>24.32453049040635</v>
       </c>
       <c r="H95" t="n">
-        <v>7.74490845224</v>
+        <v>7.751227551876691</v>
       </c>
       <c r="I95" t="n">
-        <v>3.57017802244</v>
+        <v>3.573301755446446</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.249380281769</v>
+        <v>-0.2809028850202112</v>
       </c>
       <c r="K95" t="n">
-        <v>-0.890587642319</v>
+        <v>-0.9173457264120014</v>
       </c>
       <c r="L95" t="n">
-        <v>62.18657866</v>
+        <v>62.29533164574796</v>
       </c>
       <c r="M95" t="n">
-        <v>0.154553670748</v>
+        <v>0.1379172676070128</v>
       </c>
       <c r="N95" t="n">
-        <v>3.5527136788e-15</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>0.398700119369</v>
+        <v>0.3987230591529938</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.0196757001697</v>
+        <v>0.01957001322183771</v>
       </c>
     </row>
     <row r="96">
@@ -5672,46 +5672,46 @@
         <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>0.608496651876</v>
+        <v>0.6084966518755996</v>
       </c>
       <c r="E96" t="n">
-        <v>0.608496651876</v>
+        <v>0.6084966518755989</v>
       </c>
       <c r="F96" t="n">
-        <v>0.399902779518</v>
+        <v>0.399902779518177</v>
       </c>
       <c r="G96" t="n">
-        <v>24.4069270237</v>
+        <v>24.43703637229833</v>
       </c>
       <c r="H96" t="n">
-        <v>7.73245486106</v>
+        <v>7.738818478121797</v>
       </c>
       <c r="I96" t="n">
-        <v>3.56561343676</v>
+        <v>3.568741133798148</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.285581918654</v>
+        <v>-0.3170702277743273</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.8906948974509999</v>
+        <v>-0.9174524604437726</v>
       </c>
       <c r="L96" t="n">
-        <v>62.9716670017</v>
+        <v>63.06456173754281</v>
       </c>
       <c r="M96" t="n">
-        <v>0.157776928329</v>
+        <v>0.1391109658256087</v>
       </c>
       <c r="N96" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>0.398737379894</v>
+        <v>0.3987602996100339</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.00722210899143</v>
+        <v>0.007160939466944072</v>
       </c>
     </row>
     <row r="97">
@@ -5724,46 +5724,46 @@
         <v>5</v>
       </c>
       <c r="D97" t="n">
-        <v>0.6068498221500001</v>
+        <v>0.6068498221503857</v>
       </c>
       <c r="E97" t="n">
-        <v>0.6068498221500001</v>
+        <v>0.6068498221503874</v>
       </c>
       <c r="F97" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181793</v>
       </c>
       <c r="G97" t="n">
-        <v>24.4024933764</v>
+        <v>24.40679290515585</v>
       </c>
       <c r="H97" t="n">
-        <v>7.75190933887</v>
+        <v>7.758259978504761</v>
       </c>
       <c r="I97" t="n">
-        <v>3.57292662623</v>
+        <v>3.576083265840809</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.277969430282</v>
+        <v>-0.3094638990275091</v>
       </c>
       <c r="K97" t="n">
-        <v>-0.890409537975</v>
+        <v>-0.9171642107950729</v>
       </c>
       <c r="L97" t="n">
-        <v>63.0359154687</v>
+        <v>63.15646815070367</v>
       </c>
       <c r="M97" t="n">
-        <v>0.155576991961</v>
+        <v>0.1392461569148117</v>
       </c>
       <c r="N97" t="n">
-        <v>1.7763568394e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.398735444595</v>
+        <v>0.3987584435349272</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.0266765868057</v>
+        <v>0.02660243984990807</v>
       </c>
     </row>
     <row r="98">
@@ -5776,46 +5776,46 @@
         <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>0.600320612298</v>
+        <v>0.6003206122981972</v>
       </c>
       <c r="E98" t="n">
-        <v>0.600320612298</v>
+        <v>0.6003206122981969</v>
       </c>
       <c r="F98" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181778</v>
       </c>
       <c r="G98" t="n">
-        <v>24.4582361736</v>
+        <v>24.49604972965857</v>
       </c>
       <c r="H98" t="n">
-        <v>7.71716360162</v>
+        <v>7.723539374547348</v>
       </c>
       <c r="I98" t="n">
-        <v>3.54831607067</v>
+        <v>3.551449673652947</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.251314322754</v>
+        <v>-0.282831833827617</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.890664407447</v>
+        <v>-0.9174215070880685</v>
       </c>
       <c r="L98" t="n">
-        <v>61.8823570192</v>
+        <v>61.9563665742484</v>
       </c>
       <c r="M98" t="n">
-        <v>0.157011950906</v>
+        <v>0.142680886676628</v>
       </c>
       <c r="N98" t="n">
-        <v>2.6645352591e-15</v>
+        <v>8.881784197001252e-16</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
       </c>
       <c r="P98" t="n">
-        <v>0.398622334791</v>
+        <v>0.3986453267832089</v>
       </c>
       <c r="Q98" t="n">
-        <v>-0.008069150445860001</v>
+        <v>-0.008118164107505876</v>
       </c>
     </row>
     <row r="99">
@@ -5828,46 +5828,46 @@
         <v>7</v>
       </c>
       <c r="D99" t="n">
-        <v>0.601658404376</v>
+        <v>0.6016584043757671</v>
       </c>
       <c r="E99" t="n">
-        <v>0.601658404376</v>
+        <v>0.601658404375767</v>
       </c>
       <c r="F99" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181778</v>
       </c>
       <c r="G99" t="n">
-        <v>24.3885787853</v>
+        <v>24.44033525371451</v>
       </c>
       <c r="H99" t="n">
-        <v>7.74174158749</v>
+        <v>7.748146313147848</v>
       </c>
       <c r="I99" t="n">
-        <v>3.57992520916</v>
+        <v>3.583042863848773</v>
       </c>
       <c r="J99" t="n">
-        <v>-0.256809499035</v>
+        <v>-0.2883234184306933</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.890670492047</v>
+        <v>-0.9174272443213168</v>
       </c>
       <c r="L99" t="n">
-        <v>62.2696504701</v>
+        <v>62.46455843872016</v>
       </c>
       <c r="M99" t="n">
-        <v>0.152167183849</v>
+        <v>0.1356301700628849</v>
       </c>
       <c r="N99" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>2.220446049250313e-15</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0.398711082553</v>
+        <v>0.3987340591833906</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.0165088354219</v>
+        <v>0.01648877449299491</v>
       </c>
     </row>
     <row r="100">
@@ -5880,46 +5880,46 @@
         <v>8</v>
       </c>
       <c r="D100" t="n">
-        <v>0.604006665551</v>
+        <v>0.6040066655506726</v>
       </c>
       <c r="E100" t="n">
-        <v>0.604006665551</v>
+        <v>0.6040066655506733</v>
       </c>
       <c r="F100" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181791</v>
       </c>
       <c r="G100" t="n">
-        <v>24.3321870858</v>
+        <v>24.36229643439272</v>
       </c>
       <c r="H100" t="n">
-        <v>7.73054558888</v>
+        <v>7.736843434950226</v>
       </c>
       <c r="I100" t="n">
-        <v>3.56819622839</v>
+        <v>3.571312070666953</v>
       </c>
       <c r="J100" t="n">
-        <v>-0.266110902908</v>
+        <v>-0.2976193119408372</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.890543657388</v>
+        <v>-0.9173003903625853</v>
       </c>
       <c r="L100" t="n">
-        <v>62.4436299826</v>
+        <v>62.56572640413737</v>
       </c>
       <c r="M100" t="n">
-        <v>0.152260996811</v>
+        <v>0.1380966241315297</v>
       </c>
       <c r="N100" t="n">
-        <v>8.881784196999999e-16</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.398676336627</v>
+        <v>0.3986993890598485</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.00531283680849</v>
+        <v>0.005185896295372139</v>
       </c>
     </row>
     <row r="101">
@@ -5932,46 +5932,46 @@
         <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>0.594172756924</v>
+        <v>0.594172756923902</v>
       </c>
       <c r="E101" t="n">
-        <v>0.594172756924</v>
+        <v>0.5941727569239024</v>
       </c>
       <c r="F101" t="n">
-        <v>0.399902779518</v>
+        <v>0.3999027795181784</v>
       </c>
       <c r="G101" t="n">
-        <v>24.4919030192</v>
+        <v>24.5298314571855</v>
       </c>
       <c r="H101" t="n">
-        <v>7.7195811407</v>
+        <v>7.726008080274198</v>
       </c>
       <c r="I101" t="n">
-        <v>3.55752133058</v>
+        <v>3.560650382201926</v>
       </c>
       <c r="J101" t="n">
-        <v>-0.225620925037</v>
+        <v>-0.2571602279674659</v>
       </c>
       <c r="K101" t="n">
-        <v>-0.890732770242</v>
+        <v>-0.9174899198427277</v>
       </c>
       <c r="L101" t="n">
-        <v>61.4467544283</v>
+        <v>61.58246518671323</v>
       </c>
       <c r="M101" t="n">
-        <v>0.150773866143</v>
+        <v>0.1414601937148142</v>
       </c>
       <c r="N101" t="n">
-        <v>3.5527136788e-15</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>0.398619162966</v>
+        <v>0.3986421693565738</v>
       </c>
       <c r="Q101" t="n">
-        <v>-0.00565161136789</v>
+        <v>-0.005649458380655226</v>
       </c>
     </row>
   </sheetData>
